--- a/[00] Overview/[01] Pinout Scheme/Pinouts.xlsx
+++ b/[00] Overview/[01] Pinout Scheme/Pinouts.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samue\OneDrive\Documents\[01] Projects\[01] ScratchBuiltRobotics\[00] Overview\[01] Pinout Scheme\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samue\Documents\01_Projects\01_ScratchBuiltRobotics\[00] Overview\[01] Pinout Scheme\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4BE52A2-4262-4847-8318-30493A250C41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB0757E1-37D8-4A27-B932-A6B9B9B8CD26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Standard Pins" sheetId="13" r:id="rId1"/>
@@ -962,7 +962,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="32">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -1004,108 +1004,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF434343"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFFFFFFF"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFFFFFFF"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FFFFFFFF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFFFFFFF"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FFFFFFFF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF434343"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF434343"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF434343"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF434343"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFFFFFFF"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FFFFFFFF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFFFFFFF"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFFFFFFF"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFFFFFFF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFFFFFFF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFFFFFFF"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FFFFFFFF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFFFFFFF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFFFFFFF"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFFFFFFF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFFFFFFF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FFFFFFFF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFFFFFFF"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1355,143 +1253,65 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="142">
+  <cellXfs count="133">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1501,126 +1321,126 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1628,67 +1448,118 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="14" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1922,525 +1793,525 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A1" s="118" t="s">
+      <c r="A1" s="112" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="120"/>
+      <c r="B1" s="113"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="114"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="118" t="s">
+      <c r="F1" s="112" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="120"/>
+      <c r="G1" s="113"/>
+      <c r="H1" s="113"/>
+      <c r="I1" s="114"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A2" s="121" t="s">
+      <c r="A2" s="115" t="s">
         <v>190</v>
       </c>
-      <c r="B2" s="88" t="s">
+      <c r="B2" s="62" t="s">
         <v>64</v>
       </c>
-      <c r="C2" s="53" t="s">
+      <c r="C2" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="32" t="s">
+      <c r="D2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="33">
+      <c r="E2" s="7">
         <v>1</v>
       </c>
-      <c r="F2" s="34" t="s">
+      <c r="F2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="35"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
     </row>
     <row r="3" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A3" s="122"/>
-      <c r="B3" s="88" t="s">
+      <c r="A3" s="116"/>
+      <c r="B3" s="62" t="s">
         <v>65</v>
       </c>
-      <c r="C3" s="53" t="s">
+      <c r="C3" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="32" t="s">
+      <c r="D3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="33">
+      <c r="E3" s="7">
         <v>2</v>
       </c>
-      <c r="F3" s="34" t="s">
+      <c r="F3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="35"/>
-      <c r="H3" s="43" t="s">
+      <c r="G3" s="9"/>
+      <c r="H3" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="I3" s="123" t="s">
+      <c r="I3" s="117" t="s">
         <v>192</v>
       </c>
-      <c r="L3" s="36"/>
+      <c r="L3" s="10"/>
     </row>
     <row r="4" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="33">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="7">
         <v>3</v>
       </c>
-      <c r="F4" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="H4" s="43" t="s">
+      <c r="F4" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="I4" s="115"/>
+      <c r="I4" s="107"/>
     </row>
     <row r="5" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A5" s="30"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="114" t="s">
+      <c r="A5" s="4"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="106" t="s">
         <v>59</v>
       </c>
-      <c r="D5" s="32" t="s">
+      <c r="D5" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="33">
+      <c r="E5" s="7">
         <v>4</v>
       </c>
-      <c r="F5" s="34" t="s">
+      <c r="F5" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="35"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A6" s="30"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="116"/>
-      <c r="D6" s="32" t="s">
+      <c r="A6" s="4"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="108"/>
+      <c r="D6" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="33">
+      <c r="E6" s="7">
         <v>5</v>
       </c>
-      <c r="F6" s="34" t="s">
+      <c r="F6" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="G6" s="34" t="s">
+      <c r="G6" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="43" t="s">
+      <c r="H6" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="I6" s="43" t="s">
+      <c r="I6" s="17" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A7" s="30"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="116"/>
-      <c r="D7" s="32" t="s">
+      <c r="A7" s="4"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="108"/>
+      <c r="D7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="33">
+      <c r="E7" s="7">
         <v>6</v>
       </c>
-      <c r="F7" s="38" t="s">
+      <c r="F7" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="G7" s="35"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="115"/>
-      <c r="D8" s="32" t="s">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="107"/>
+      <c r="D8" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E8" s="33">
+      <c r="E8" s="7">
         <v>7</v>
       </c>
-      <c r="F8" s="39" t="s">
+      <c r="F8" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="G8" s="51" t="s">
+      <c r="G8" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="H8" s="95" t="s">
+      <c r="H8" s="69" t="s">
         <v>224</v>
       </c>
-      <c r="I8" s="8"/>
+      <c r="I8" s="2"/>
     </row>
     <row r="9" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" s="33">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="7">
         <v>8</v>
       </c>
-      <c r="F9" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
+      <c r="F9" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
     </row>
     <row r="10" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A10" s="107" t="s">
+      <c r="A10" s="81" t="s">
         <v>73</v>
       </c>
-      <c r="B10" s="141" t="s">
+      <c r="B10" s="88" t="s">
         <v>193</v>
       </c>
-      <c r="C10" s="132" t="s">
+      <c r="C10" s="110" t="s">
         <v>60</v>
       </c>
-      <c r="D10" s="32" t="s">
+      <c r="D10" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="E10" s="33">
+      <c r="E10" s="7">
         <v>9</v>
       </c>
-      <c r="F10" s="39" t="s">
+      <c r="F10" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="G10" s="51" t="s">
+      <c r="G10" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="H10" s="95" t="s">
+      <c r="H10" s="69" t="s">
         <v>223</v>
       </c>
-      <c r="I10" s="8"/>
+      <c r="I10" s="2"/>
     </row>
     <row r="11" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A11" s="110" t="s">
+      <c r="A11" s="84" t="s">
         <v>73</v>
       </c>
-      <c r="B11" s="95" t="s">
+      <c r="B11" s="69" t="s">
         <v>221</v>
       </c>
-      <c r="C11" s="133"/>
-      <c r="D11" s="32" t="s">
+      <c r="C11" s="111"/>
+      <c r="D11" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="E11" s="33">
+      <c r="E11" s="7">
         <v>10</v>
       </c>
-      <c r="F11" s="39" t="s">
+      <c r="F11" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="51" t="s">
+      <c r="G11" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="H11" s="95" t="s">
+      <c r="H11" s="69" t="s">
         <v>222</v>
       </c>
-      <c r="I11" s="8"/>
+      <c r="I11" s="2"/>
     </row>
     <row r="12" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A12" s="54"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="116"/>
-      <c r="D12" s="32" t="s">
+      <c r="A12" s="28"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="108"/>
+      <c r="D12" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="E12" s="33">
+      <c r="E12" s="7">
         <v>11</v>
       </c>
-      <c r="F12" s="34" t="s">
+      <c r="F12" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="G12" s="35"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
     </row>
     <row r="13" spans="1:12" ht="15.75" customHeight="1">
-      <c r="C13" s="115"/>
-      <c r="D13" s="32" t="s">
+      <c r="C13" s="107"/>
+      <c r="D13" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E13" s="33">
-        <v>12</v>
-      </c>
-      <c r="F13" s="39" t="s">
+      <c r="E13" s="7">
+        <v>12</v>
+      </c>
+      <c r="F13" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="G13" s="41"/>
-      <c r="H13" s="43" t="s">
+      <c r="G13" s="15"/>
+      <c r="H13" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="I13" s="43" t="s">
+      <c r="I13" s="17" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" s="33">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" s="7">
         <v>13</v>
       </c>
-      <c r="F14" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="G14" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
+      <c r="F14" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
     </row>
     <row r="15" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A15" s="114" t="s">
+      <c r="A15" s="106" t="s">
         <v>102</v>
       </c>
-      <c r="B15" s="43" t="s">
+      <c r="B15" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="C15" s="114" t="s">
+      <c r="C15" s="106" t="s">
         <v>61</v>
       </c>
-      <c r="D15" s="32" t="s">
+      <c r="D15" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="E15" s="33">
+      <c r="E15" s="7">
         <v>14</v>
       </c>
-      <c r="F15" s="39" t="s">
+      <c r="F15" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="G15" s="114" t="s">
+      <c r="G15" s="106" t="s">
         <v>62</v>
       </c>
-      <c r="H15" s="43" t="s">
+      <c r="H15" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="I15" s="114" t="s">
+      <c r="I15" s="106" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A16" s="115"/>
-      <c r="B16" s="43" t="s">
+      <c r="A16" s="107"/>
+      <c r="B16" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="C16" s="116"/>
-      <c r="D16" s="39" t="s">
+      <c r="C16" s="108"/>
+      <c r="D16" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="E16" s="33">
+      <c r="E16" s="7">
         <v>15</v>
       </c>
-      <c r="F16" s="39" t="s">
+      <c r="F16" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="G16" s="115"/>
-      <c r="H16" s="43" t="s">
+      <c r="G16" s="107"/>
+      <c r="H16" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="I16" s="117"/>
+      <c r="I16" s="109"/>
     </row>
     <row r="17" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A17" s="114" t="s">
+      <c r="A17" s="106" t="s">
         <v>102</v>
       </c>
-      <c r="B17" s="43" t="s">
+      <c r="B17" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="C17" s="116"/>
-      <c r="D17" s="39" t="s">
+      <c r="C17" s="108"/>
+      <c r="D17" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="E17" s="33">
+      <c r="E17" s="7">
         <v>16</v>
       </c>
-      <c r="F17" s="39" t="s">
+      <c r="F17" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="G17" s="42" t="s">
+      <c r="G17" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="H17" s="8"/>
-      <c r="I17" s="54"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="28"/>
     </row>
     <row r="18" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A18" s="115"/>
-      <c r="B18" s="43" t="s">
+      <c r="A18" s="107"/>
+      <c r="B18" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="C18" s="115"/>
-      <c r="D18" s="32" t="s">
+      <c r="C18" s="107"/>
+      <c r="D18" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E18" s="33">
+      <c r="E18" s="7">
         <v>17</v>
       </c>
-      <c r="F18" s="39" t="s">
+      <c r="F18" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="G18" s="42" t="s">
+      <c r="G18" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="H18" s="8"/>
-      <c r="I18" s="54"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="28"/>
     </row>
     <row r="19" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="D19" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="E19" s="33">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" s="7">
         <v>18</v>
       </c>
-      <c r="F19" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="G19" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8"/>
+      <c r="F19" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
     </row>
     <row r="20" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="31" t="s">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D20" s="32" t="s">
+      <c r="D20" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="E20" s="33">
+      <c r="E20" s="7">
         <v>19</v>
       </c>
-      <c r="F20" s="39" t="s">
+      <c r="F20" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="G20" s="42" t="s">
+      <c r="G20" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="H20" s="43" t="s">
+      <c r="H20" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="I20" s="43" t="s">
+      <c r="I20" s="17" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="31" t="s">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D21" s="32" t="s">
+      <c r="D21" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E21" s="33">
+      <c r="E21" s="7">
         <v>20</v>
       </c>
-      <c r="F21" s="39" t="s">
+      <c r="F21" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="G21" s="42" t="s">
+      <c r="G21" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="H21" s="43" t="s">
+      <c r="H21" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="I21" s="43" t="s">
+      <c r="I21" s="17" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="12.75">
-      <c r="C23" s="44"/>
+      <c r="C23" s="18"/>
     </row>
     <row r="24" spans="1:9" ht="12.75">
-      <c r="C24" s="111"/>
-      <c r="D24" s="111"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="111"/>
-      <c r="G24" s="112"/>
-      <c r="H24" s="113"/>
+      <c r="C24" s="85"/>
+      <c r="D24" s="85"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="85"/>
+      <c r="G24" s="86"/>
+      <c r="H24" s="87"/>
     </row>
     <row r="25" spans="1:9" ht="12.75">
-      <c r="C25" s="111"/>
-      <c r="D25" s="111"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="111"/>
+      <c r="C25" s="85"/>
+      <c r="D25" s="85"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="85"/>
       <c r="G25" s="1"/>
-      <c r="H25" s="113"/>
+      <c r="H25" s="87"/>
     </row>
     <row r="26" spans="1:9" ht="12.75">
-      <c r="C26" s="29"/>
-      <c r="D26" s="29"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="111"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="85"/>
       <c r="G26" s="1"/>
-      <c r="H26" s="113"/>
+      <c r="H26" s="87"/>
     </row>
     <row r="27" spans="1:9" ht="12.75">
-      <c r="C27" s="29"/>
-      <c r="D27" s="29"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="111"/>
-      <c r="G27" s="30"/>
-      <c r="H27" s="113"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="85"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="87"/>
     </row>
     <row r="28" spans="1:9" ht="12.75">
-      <c r="C28" s="29"/>
-      <c r="D28" s="29"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="111"/>
-      <c r="G28" s="29"/>
-      <c r="H28" s="113"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="85"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="87"/>
     </row>
     <row r="29" spans="1:9" ht="12.75">
-      <c r="C29" s="29"/>
-      <c r="D29" s="29"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="111"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="85"/>
       <c r="G29" s="1"/>
-      <c r="H29" s="113"/>
+      <c r="H29" s="87"/>
     </row>
     <row r="30" spans="1:9" ht="12.75">
-      <c r="C30" s="29"/>
-      <c r="D30" s="29"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="111"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="85"/>
       <c r="G30" s="1"/>
-      <c r="H30" s="113"/>
+      <c r="H30" s="87"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -2481,511 +2352,511 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="118" t="s">
+      <c r="A1" s="112" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="120"/>
+      <c r="B1" s="113"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="114"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="118" t="s">
+      <c r="F1" s="112" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="120"/>
-      <c r="K1" s="97" t="s">
+      <c r="G1" s="113"/>
+      <c r="H1" s="113"/>
+      <c r="I1" s="114"/>
+      <c r="K1" s="71" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="121" t="s">
+      <c r="A2" s="115" t="s">
         <v>190</v>
       </c>
-      <c r="B2" s="88" t="s">
+      <c r="B2" s="62" t="s">
         <v>64</v>
       </c>
-      <c r="C2" s="31" t="s">
+      <c r="C2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="32" t="s">
+      <c r="D2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="33">
+      <c r="E2" s="7">
         <v>1</v>
       </c>
-      <c r="F2" s="34" t="s">
+      <c r="F2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="35"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="122"/>
-      <c r="B3" s="88" t="s">
+      <c r="A3" s="116"/>
+      <c r="B3" s="62" t="s">
         <v>65</v>
       </c>
-      <c r="C3" s="87" t="s">
+      <c r="C3" s="61" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="32" t="s">
+      <c r="D3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="33">
+      <c r="E3" s="7">
         <v>2</v>
       </c>
-      <c r="F3" s="34" t="s">
+      <c r="F3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="35"/>
-      <c r="H3" s="43" t="s">
+      <c r="G3" s="9"/>
+      <c r="H3" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="I3" s="123" t="s">
+      <c r="I3" s="117" t="s">
         <v>192</v>
       </c>
-      <c r="K3" s="97" t="s">
+      <c r="K3" s="71" t="s">
         <v>207</v>
       </c>
-      <c r="L3" s="97"/>
+      <c r="L3" s="71"/>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="33">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="7">
         <v>3</v>
       </c>
-      <c r="F4" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="H4" s="43" t="s">
+      <c r="F4" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="I4" s="115"/>
-      <c r="K4" s="96" t="s">
+      <c r="I4" s="107"/>
+      <c r="K4" s="70" t="s">
         <v>66</v>
       </c>
-      <c r="L4" s="96" t="s">
+      <c r="L4" s="70" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" s="30"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="114" t="s">
+      <c r="A5" s="4"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="106" t="s">
         <v>59</v>
       </c>
-      <c r="D5" s="32" t="s">
+      <c r="D5" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="33">
+      <c r="E5" s="7">
         <v>4</v>
       </c>
-      <c r="F5" s="34" t="s">
+      <c r="F5" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="35"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
-      <c r="K5" s="105" t="s">
+      <c r="G5" s="9"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="K5" s="79" t="s">
         <v>80</v>
       </c>
-      <c r="L5" s="105" t="s">
+      <c r="L5" s="79" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" s="30"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="116"/>
-      <c r="D6" s="32" t="s">
+      <c r="A6" s="4"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="108"/>
+      <c r="D6" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="33">
+      <c r="E6" s="7">
         <v>5</v>
       </c>
-      <c r="F6" s="34" t="s">
+      <c r="F6" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="G6" s="34" t="s">
+      <c r="G6" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="89" t="s">
+      <c r="H6" s="63" t="s">
         <v>202</v>
       </c>
-      <c r="I6" s="89" t="s">
+      <c r="I6" s="63" t="s">
         <v>213</v>
       </c>
-      <c r="K6" s="96" t="s">
+      <c r="K6" s="70" t="s">
         <v>54</v>
       </c>
-      <c r="L6" s="96" t="s">
+      <c r="L6" s="70" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:12">
-      <c r="A7" s="30"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="116"/>
-      <c r="D7" s="32" t="s">
+      <c r="A7" s="4"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="108"/>
+      <c r="D7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="33">
+      <c r="E7" s="7">
         <v>6</v>
       </c>
-      <c r="F7" s="38" t="s">
+      <c r="F7" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="G7" s="35"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="K7" s="96" t="s">
+      <c r="G7" s="9"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="K7" s="70" t="s">
         <v>215</v>
       </c>
-      <c r="L7" s="96" t="s">
+      <c r="L7" s="70" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:12">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="115"/>
-      <c r="D8" s="32" t="s">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="107"/>
+      <c r="D8" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E8" s="33">
+      <c r="E8" s="7">
         <v>7</v>
       </c>
-      <c r="F8" s="39" t="s">
+      <c r="F8" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="G8" s="38" t="s">
+      <c r="G8" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="K8" s="96" t="s">
-        <v>12</v>
-      </c>
-      <c r="L8" s="96" t="s">
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="K8" s="70" t="s">
+        <v>12</v>
+      </c>
+      <c r="L8" s="70" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:12">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" s="33">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="7">
         <v>8</v>
       </c>
-      <c r="F9" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
+      <c r="F9" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
     </row>
     <row r="10" spans="1:12">
-      <c r="A10" s="43" t="s">
+      <c r="A10" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="B10" s="89" t="s">
+      <c r="B10" s="63" t="s">
         <v>193</v>
       </c>
-      <c r="C10" s="114" t="s">
+      <c r="C10" s="106" t="s">
         <v>60</v>
       </c>
-      <c r="D10" s="32" t="s">
+      <c r="D10" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="E10" s="33">
+      <c r="E10" s="7">
         <v>9</v>
       </c>
-      <c r="F10" s="39" t="s">
+      <c r="F10" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="G10" s="38" t="s">
+      <c r="G10" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="K10" s="103" t="s">
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="K10" s="77" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="11" spans="1:12">
-      <c r="A11" s="54"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="116"/>
-      <c r="D11" s="32" t="s">
+      <c r="A11" s="28"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="108"/>
+      <c r="D11" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="E11" s="33">
+      <c r="E11" s="7">
         <v>10</v>
       </c>
-      <c r="F11" s="39" t="s">
+      <c r="F11" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="38" t="s">
+      <c r="G11" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="K11" s="96" t="s">
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="K11" s="70" t="s">
         <v>5</v>
       </c>
-      <c r="L11" s="96" t="s">
+      <c r="L11" s="70" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:12">
-      <c r="A12" s="54"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="116"/>
-      <c r="D12" s="32" t="s">
+      <c r="A12" s="28"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="108"/>
+      <c r="D12" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="E12" s="33">
+      <c r="E12" s="7">
         <v>11</v>
       </c>
-      <c r="F12" s="34" t="s">
+      <c r="F12" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="G12" s="35"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="K12" s="96" t="s">
+      <c r="G12" s="9"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="K12" s="70" t="s">
         <v>10</v>
       </c>
-      <c r="L12" s="96" t="s">
+      <c r="L12" s="70" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:12">
-      <c r="C13" s="115"/>
-      <c r="D13" s="32" t="s">
+      <c r="C13" s="107"/>
+      <c r="D13" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E13" s="33">
-        <v>12</v>
-      </c>
-      <c r="F13" s="39" t="s">
+      <c r="E13" s="7">
+        <v>12</v>
+      </c>
+      <c r="F13" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="G13" s="41"/>
-      <c r="H13" s="43" t="s">
+      <c r="G13" s="15"/>
+      <c r="H13" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="I13" s="43" t="s">
+      <c r="I13" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="K13" s="96" t="s">
-        <v>12</v>
-      </c>
-      <c r="L13" s="96" t="s">
+      <c r="K13" s="70" t="s">
+        <v>12</v>
+      </c>
+      <c r="L13" s="70" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:12">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="85" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" s="33">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="59" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" s="7">
         <v>13</v>
       </c>
-      <c r="F14" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="G14" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
-      <c r="K14" s="96" t="s">
+      <c r="F14" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="K14" s="70" t="s">
         <v>202</v>
       </c>
-      <c r="L14" s="96" t="s">
+      <c r="L14" s="70" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="15" spans="1:12">
-      <c r="C15" s="137" t="s">
+      <c r="C15" s="129" t="s">
         <v>61</v>
       </c>
-      <c r="D15" s="83" t="s">
+      <c r="D15" s="57" t="s">
         <v>43</v>
       </c>
-      <c r="E15" s="33">
+      <c r="E15" s="7">
         <v>14</v>
       </c>
-      <c r="F15" s="39" t="s">
+      <c r="F15" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="G15" s="114" t="s">
+      <c r="G15" s="106" t="s">
         <v>62</v>
       </c>
-      <c r="H15" s="43" t="s">
+      <c r="H15" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="I15" s="134" t="s">
+      <c r="I15" s="126" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="16" spans="1:12">
-      <c r="C16" s="138"/>
-      <c r="D16" s="84" t="s">
+      <c r="C16" s="130"/>
+      <c r="D16" s="58" t="s">
         <v>46</v>
       </c>
-      <c r="E16" s="33">
+      <c r="E16" s="7">
         <v>15</v>
       </c>
-      <c r="F16" s="39" t="s">
+      <c r="F16" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="G16" s="115"/>
-      <c r="H16" s="43" t="s">
+      <c r="G16" s="107"/>
+      <c r="H16" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="I16" s="115"/>
+      <c r="I16" s="107"/>
     </row>
     <row r="17" spans="1:9">
-      <c r="C17" s="138"/>
-      <c r="D17" s="84" t="s">
+      <c r="C17" s="130"/>
+      <c r="D17" s="58" t="s">
         <v>48</v>
       </c>
-      <c r="E17" s="33">
+      <c r="E17" s="7">
         <v>16</v>
       </c>
-      <c r="F17" s="39" t="s">
+      <c r="F17" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="G17" s="42" t="s">
+      <c r="G17" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="H17" s="8"/>
-      <c r="I17" s="54"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="28"/>
     </row>
     <row r="18" spans="1:9">
-      <c r="C18" s="138"/>
-      <c r="D18" s="83" t="s">
+      <c r="C18" s="130"/>
+      <c r="D18" s="57" t="s">
         <v>50</v>
       </c>
-      <c r="E18" s="33">
+      <c r="E18" s="7">
         <v>17</v>
       </c>
-      <c r="F18" s="39" t="s">
+      <c r="F18" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="G18" s="42" t="s">
+      <c r="G18" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="H18" s="8"/>
-      <c r="I18" s="54"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="28"/>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="86" t="s">
-        <v>12</v>
-      </c>
-      <c r="D19" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="E19" s="33">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="60" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" s="7">
         <v>18</v>
       </c>
-      <c r="F19" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="G19" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8"/>
+      <c r="F19" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="139" t="s">
+      <c r="A20" s="131" t="s">
         <v>189</v>
       </c>
-      <c r="B20" s="88" t="s">
+      <c r="B20" s="62" t="s">
         <v>64</v>
       </c>
-      <c r="C20" s="53" t="s">
+      <c r="C20" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="D20" s="32" t="s">
+      <c r="D20" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="E20" s="33">
+      <c r="E20" s="7">
         <v>19</v>
       </c>
-      <c r="F20" s="39" t="s">
+      <c r="F20" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="G20" s="42" t="s">
+      <c r="G20" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="H20" s="43" t="s">
+      <c r="H20" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="I20" s="43" t="s">
+      <c r="I20" s="17" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="140"/>
-      <c r="B21" s="88" t="s">
+      <c r="A21" s="132"/>
+      <c r="B21" s="62" t="s">
         <v>65</v>
       </c>
-      <c r="C21" s="53" t="s">
+      <c r="C21" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="D21" s="32" t="s">
+      <c r="D21" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E21" s="33">
+      <c r="E21" s="7">
         <v>20</v>
       </c>
-      <c r="F21" s="39" t="s">
+      <c r="F21" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="G21" s="42" t="s">
+      <c r="G21" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="H21" s="43" t="s">
+      <c r="H21" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="I21" s="43" t="s">
+      <c r="I21" s="17" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="C23" s="44"/>
+      <c r="C23" s="18"/>
     </row>
     <row r="26" spans="1:9">
-      <c r="C26" s="77" t="s">
+      <c r="C26" s="51" t="s">
         <v>191</v>
       </c>
     </row>
@@ -3021,215 +2892,215 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="12.75">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="C1" s="30" t="s">
+      <c r="C1" s="4" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A2" s="30"/>
-      <c r="B2" s="30" t="s">
+      <c r="A2" s="4"/>
+      <c r="B2" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="D2" s="30" t="s">
+      <c r="D2" s="4" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A3" s="66">
+      <c r="A3" s="40">
         <v>1</v>
       </c>
-      <c r="B3" s="47" t="s">
+      <c r="B3" s="21" t="s">
         <v>144</v>
       </c>
-      <c r="C3" s="47" t="s">
+      <c r="C3" s="21" t="s">
         <v>145</v>
       </c>
-      <c r="D3" s="47" t="s">
+      <c r="D3" s="21" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A4" s="66">
+      <c r="A4" s="40">
         <v>2</v>
       </c>
-      <c r="B4" s="47" t="s">
+      <c r="B4" s="21" t="s">
         <v>146</v>
       </c>
-      <c r="C4" s="47" t="s">
+      <c r="C4" s="21" t="s">
         <v>147</v>
       </c>
-      <c r="D4" s="47" t="s">
+      <c r="D4" s="21" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A5" s="66">
+      <c r="A5" s="40">
         <v>3</v>
       </c>
-      <c r="B5" s="47" t="s">
+      <c r="B5" s="21" t="s">
         <v>149</v>
       </c>
-      <c r="C5" s="47" t="s">
+      <c r="C5" s="21" t="s">
         <v>150</v>
       </c>
-      <c r="D5" s="47" t="s">
+      <c r="D5" s="21" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A6" s="66">
+      <c r="A6" s="40">
         <v>4</v>
       </c>
-      <c r="B6" s="47" t="s">
+      <c r="B6" s="21" t="s">
         <v>152</v>
       </c>
-      <c r="C6" s="47" t="s">
+      <c r="C6" s="21" t="s">
         <v>153</v>
       </c>
-      <c r="D6" s="47" t="s">
+      <c r="D6" s="21" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A7" s="66">
+      <c r="A7" s="40">
         <v>5</v>
       </c>
-      <c r="B7" s="47" t="s">
+      <c r="B7" s="21" t="s">
         <v>154</v>
       </c>
-      <c r="C7" s="47" t="s">
+      <c r="C7" s="21" t="s">
         <v>155</v>
       </c>
-      <c r="D7" s="47" t="s">
+      <c r="D7" s="21" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A8" s="66">
+      <c r="A8" s="40">
         <v>6</v>
       </c>
-      <c r="B8" s="50" t="s">
+      <c r="B8" s="24" t="s">
         <v>157</v>
       </c>
-      <c r="C8" s="50" t="s">
+      <c r="C8" s="24" t="s">
         <v>158</v>
       </c>
-      <c r="D8" s="50" t="s">
+      <c r="D8" s="24" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A9" s="66">
+      <c r="A9" s="40">
         <v>7</v>
       </c>
-      <c r="B9" s="50" t="s">
+      <c r="B9" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="C9" s="50" t="s">
+      <c r="C9" s="24" t="s">
         <v>159</v>
       </c>
-      <c r="D9" s="50" t="s">
+      <c r="D9" s="24" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A10" s="66">
+      <c r="A10" s="40">
         <v>8</v>
       </c>
-      <c r="B10" s="50" t="s">
+      <c r="B10" s="24" t="s">
         <v>160</v>
       </c>
-      <c r="C10" s="50" t="s">
+      <c r="C10" s="24" t="s">
         <v>161</v>
       </c>
-      <c r="D10" s="50" t="s">
+      <c r="D10" s="24" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A11" s="66">
+      <c r="A11" s="40">
         <v>9</v>
       </c>
-      <c r="B11" s="50" t="s">
+      <c r="B11" s="24" t="s">
         <v>163</v>
       </c>
-      <c r="C11" s="50" t="s">
+      <c r="C11" s="24" t="s">
         <v>164</v>
       </c>
-      <c r="D11" s="50" t="s">
+      <c r="D11" s="24" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A12" s="66">
+      <c r="A12" s="40">
         <v>10</v>
       </c>
-      <c r="B12" s="50" t="s">
+      <c r="B12" s="24" t="s">
         <v>166</v>
       </c>
-      <c r="C12" s="50" t="s">
+      <c r="C12" s="24" t="s">
         <v>167</v>
       </c>
-      <c r="D12" s="50" t="s">
+      <c r="D12" s="24" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A13" s="66">
+      <c r="A13" s="40">
         <v>11</v>
       </c>
-      <c r="B13" s="50" t="s">
+      <c r="B13" s="24" t="s">
         <v>168</v>
       </c>
-      <c r="C13" s="50" t="s">
+      <c r="C13" s="24" t="s">
         <v>169</v>
       </c>
-      <c r="D13" s="50" t="s">
+      <c r="D13" s="24" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A14" s="66">
-        <v>12</v>
-      </c>
-      <c r="B14" s="50" t="s">
+      <c r="A14" s="40">
+        <v>12</v>
+      </c>
+      <c r="B14" s="24" t="s">
         <v>101</v>
       </c>
-      <c r="C14" s="50" t="s">
+      <c r="C14" s="24" t="s">
         <v>101</v>
       </c>
-      <c r="D14" s="50" t="s">
+      <c r="D14" s="24" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A15" s="66">
+      <c r="A15" s="40">
         <v>13</v>
       </c>
-      <c r="B15" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="D15" s="46" t="s">
+      <c r="B15" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" s="20" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A16" s="66">
+      <c r="A16" s="40">
         <v>14</v>
       </c>
-      <c r="B16" s="45" t="s">
+      <c r="B16" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="C16" s="45" t="s">
+      <c r="C16" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="D16" s="45" t="s">
+      <c r="D16" s="19" t="s">
         <v>170</v>
       </c>
     </row>
@@ -3251,187 +3122,187 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="48" t="s">
         <v>180</v>
       </c>
-      <c r="C1" s="30"/>
+      <c r="C1" s="4"/>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="30"/>
-      <c r="B2" s="30" t="s">
+      <c r="A2" s="4"/>
+      <c r="B2" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="D2" s="30" t="s">
+      <c r="D2" s="4" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="66">
+      <c r="A3" s="40">
         <v>1</v>
       </c>
-      <c r="B3" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="79" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="79" t="s">
+      <c r="B3" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="53" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="53" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="66">
+      <c r="A4" s="40">
         <v>2</v>
       </c>
-      <c r="B4" s="45" t="s">
+      <c r="B4" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="C4" s="80" t="s">
+      <c r="C4" s="54" t="s">
         <v>79</v>
       </c>
-      <c r="D4" s="80" t="s">
+      <c r="D4" s="54" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="66">
+      <c r="A5" s="40">
         <v>3</v>
       </c>
-      <c r="B5" s="75" t="s">
+      <c r="B5" s="49" t="s">
         <v>160</v>
       </c>
-      <c r="C5" s="47"/>
-      <c r="D5" s="75" t="s">
+      <c r="C5" s="21"/>
+      <c r="D5" s="49" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="66">
+      <c r="A6" s="40">
         <v>4</v>
       </c>
-      <c r="B6" s="75" t="s">
+      <c r="B6" s="49" t="s">
         <v>64</v>
       </c>
-      <c r="C6" s="75" t="s">
+      <c r="C6" s="49" t="s">
         <v>187</v>
       </c>
-      <c r="D6" s="75" t="s">
+      <c r="D6" s="49" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="66">
+      <c r="A7" s="40">
         <v>5</v>
       </c>
-      <c r="B7" s="75" t="s">
+      <c r="B7" s="49" t="s">
         <v>168</v>
       </c>
-      <c r="C7" s="47"/>
-      <c r="D7" s="75" t="s">
+      <c r="C7" s="21"/>
+      <c r="D7" s="49" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="66">
+      <c r="A8" s="40">
         <v>6</v>
       </c>
-      <c r="B8" s="81" t="s">
+      <c r="B8" s="55" t="s">
         <v>182</v>
       </c>
-      <c r="C8" s="82"/>
-      <c r="D8" s="81" t="s">
+      <c r="C8" s="56"/>
+      <c r="D8" s="55" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="66">
+      <c r="A9" s="40">
         <v>7</v>
       </c>
-      <c r="B9" s="81" t="s">
+      <c r="B9" s="55" t="s">
         <v>101</v>
       </c>
-      <c r="C9" s="82"/>
-      <c r="D9" s="81" t="s">
+      <c r="C9" s="56"/>
+      <c r="D9" s="55" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="66">
+      <c r="A10" s="40">
         <v>8</v>
       </c>
-      <c r="B10" s="81" t="s">
+      <c r="B10" s="55" t="s">
         <v>181</v>
       </c>
-      <c r="C10" s="82"/>
-      <c r="D10" s="81" t="s">
+      <c r="C10" s="56"/>
+      <c r="D10" s="55" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="66">
+      <c r="A11" s="40">
         <v>9</v>
       </c>
-      <c r="B11" s="76" t="s">
+      <c r="B11" s="50" t="s">
         <v>181</v>
       </c>
-      <c r="C11" s="50"/>
-      <c r="D11" s="50"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="24"/>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="66">
+      <c r="A12" s="40">
         <v>10</v>
       </c>
-      <c r="B12" s="76" t="s">
+      <c r="B12" s="50" t="s">
         <v>183</v>
       </c>
-      <c r="C12" s="50"/>
-      <c r="D12" s="50"/>
-      <c r="E12" s="77" t="s">
+      <c r="C12" s="24"/>
+      <c r="D12" s="24"/>
+      <c r="E12" s="51" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="66">
+      <c r="A13" s="40">
         <v>11</v>
       </c>
-      <c r="B13" s="76" t="s">
+      <c r="B13" s="50" t="s">
         <v>184</v>
       </c>
-      <c r="C13" s="50"/>
-      <c r="D13" s="50"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="24"/>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="66">
-        <v>12</v>
-      </c>
-      <c r="B14" s="76" t="s">
+      <c r="A14" s="40">
+        <v>12</v>
+      </c>
+      <c r="B14" s="50" t="s">
         <v>185</v>
       </c>
-      <c r="C14" s="50"/>
-      <c r="D14" s="50"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="24"/>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="66">
+      <c r="A15" s="40">
         <v>13</v>
       </c>
-      <c r="B15" s="78" t="s">
+      <c r="B15" s="52" t="s">
         <v>186</v>
       </c>
-      <c r="C15" s="50"/>
-      <c r="D15" s="50"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="24"/>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="66">
+      <c r="A16" s="40">
         <v>14</v>
       </c>
-      <c r="B16" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C16" s="46"/>
-      <c r="D16" s="46"/>
+      <c r="B16" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
     </row>
     <row r="21" spans="3:3">
-      <c r="C21" s="77"/>
+      <c r="C21" s="51"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3452,197 +3323,197 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A1" s="55"/>
-      <c r="B1" s="37" t="s">
+      <c r="A1" s="29"/>
+      <c r="B1" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="C1" s="33"/>
-      <c r="D1" s="37" t="s">
+      <c r="C1" s="7"/>
+      <c r="D1" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="E1" s="56"/>
-      <c r="F1" s="46" t="s">
+      <c r="E1" s="30"/>
+      <c r="F1" s="20" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A2" s="57"/>
-      <c r="B2" s="58" t="s">
+      <c r="A2" s="31"/>
+      <c r="B2" s="32" t="s">
         <v>117</v>
       </c>
-      <c r="C2" s="33">
+      <c r="C2" s="7">
         <v>1</v>
       </c>
-      <c r="D2" s="59" t="s">
+      <c r="D2" s="33" t="s">
         <v>118</v>
       </c>
-      <c r="E2" s="60" t="s">
+      <c r="E2" s="34" t="s">
         <v>119</v>
       </c>
-      <c r="F2" s="50" t="s">
+      <c r="F2" s="24" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A3" s="61" t="s">
+      <c r="A3" s="35" t="s">
         <v>121</v>
       </c>
-      <c r="B3" s="61" t="s">
+      <c r="B3" s="35" t="s">
         <v>122</v>
       </c>
-      <c r="C3" s="33">
+      <c r="C3" s="7">
         <v>2</v>
       </c>
-      <c r="D3" s="59" t="s">
+      <c r="D3" s="33" t="s">
         <v>123</v>
       </c>
-      <c r="E3" s="60" t="s">
+      <c r="E3" s="34" t="s">
         <v>124</v>
       </c>
-      <c r="F3" s="50" t="s">
+      <c r="F3" s="24" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A4" s="61" t="s">
+      <c r="A4" s="35" t="s">
         <v>126</v>
       </c>
-      <c r="B4" s="61" t="s">
+      <c r="B4" s="35" t="s">
         <v>127</v>
       </c>
-      <c r="C4" s="33">
+      <c r="C4" s="7">
         <v>3</v>
       </c>
-      <c r="D4" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="62"/>
-      <c r="F4" s="49"/>
+      <c r="D4" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="36"/>
+      <c r="F4" s="23"/>
     </row>
     <row r="5" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A5" s="61" t="s">
+      <c r="A5" s="35" t="s">
         <v>128</v>
       </c>
-      <c r="B5" s="61" t="s">
+      <c r="B5" s="35" t="s">
         <v>129</v>
       </c>
-      <c r="C5" s="33">
+      <c r="C5" s="7">
         <v>4</v>
       </c>
-      <c r="D5" s="63" t="s">
+      <c r="D5" s="37" t="s">
         <v>79</v>
       </c>
-      <c r="E5" s="73" t="s">
+      <c r="E5" s="47" t="s">
         <v>130</v>
       </c>
-      <c r="F5" s="49"/>
+      <c r="F5" s="23"/>
     </row>
     <row r="6" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A6" s="61" t="s">
+      <c r="A6" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="B6" s="61" t="s">
+      <c r="B6" s="35" t="s">
         <v>132</v>
       </c>
-      <c r="C6" s="33">
+      <c r="C6" s="7">
         <v>5</v>
       </c>
-      <c r="D6" s="59" t="s">
+      <c r="D6" s="33" t="s">
         <v>133</v>
       </c>
-      <c r="E6" s="60" t="s">
+      <c r="E6" s="34" t="s">
         <v>134</v>
       </c>
-      <c r="F6" s="50" t="s">
+      <c r="F6" s="24" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A7" s="64"/>
-      <c r="B7" s="65" t="s">
+      <c r="A7" s="38"/>
+      <c r="B7" s="39" t="s">
         <v>136</v>
       </c>
-      <c r="C7" s="33">
+      <c r="C7" s="7">
         <v>6</v>
       </c>
-      <c r="D7" s="59" t="s">
+      <c r="D7" s="33" t="s">
         <v>137</v>
       </c>
-      <c r="E7" s="60" t="s">
+      <c r="E7" s="34" t="s">
         <v>138</v>
       </c>
-      <c r="F7" s="50" t="s">
+      <c r="F7" s="24" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A9" s="30"/>
+      <c r="A9" s="4"/>
     </row>
     <row r="10" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A10" s="30"/>
+      <c r="A10" s="4"/>
     </row>
     <row r="11" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A11" s="67" t="s">
+      <c r="A11" s="41" t="s">
         <v>171</v>
       </c>
-      <c r="B11" s="67" t="s">
+      <c r="B11" s="41" t="s">
         <v>172</v>
       </c>
-      <c r="C11" s="68"/>
-      <c r="D11" s="69" t="s">
+      <c r="C11" s="42"/>
+      <c r="D11" s="43" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A12" s="70" t="s">
+      <c r="A12" s="44" t="s">
         <v>174</v>
       </c>
-      <c r="B12" s="70" t="s">
+      <c r="B12" s="44" t="s">
         <v>174</v>
       </c>
-      <c r="C12" s="71"/>
-      <c r="D12" s="72" t="s">
+      <c r="C12" s="45"/>
+      <c r="D12" s="46" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A13" s="70" t="s">
+      <c r="A13" s="44" t="s">
         <v>176</v>
       </c>
-      <c r="B13" s="70" t="s">
+      <c r="B13" s="44" t="s">
         <v>174</v>
       </c>
-      <c r="C13" s="71"/>
-      <c r="D13" s="72" t="s">
+      <c r="C13" s="45"/>
+      <c r="D13" s="46" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A14" s="70" t="s">
+      <c r="A14" s="44" t="s">
         <v>174</v>
       </c>
-      <c r="B14" s="70" t="s">
+      <c r="B14" s="44" t="s">
         <v>176</v>
       </c>
-      <c r="C14" s="71"/>
-      <c r="D14" s="72" t="s">
+      <c r="C14" s="45"/>
+      <c r="D14" s="46" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A15" s="70" t="s">
+      <c r="A15" s="44" t="s">
         <v>176</v>
       </c>
-      <c r="B15" s="70" t="s">
+      <c r="B15" s="44" t="s">
         <v>176</v>
       </c>
-      <c r="C15" s="71"/>
-      <c r="D15" s="72" t="s">
+      <c r="C15" s="45"/>
+      <c r="D15" s="46" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A16" s="30" t="s">
+      <c r="A16" s="4" t="s">
         <v>179</v>
       </c>
     </row>
@@ -3667,475 +3538,475 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A1" s="124" t="s">
+      <c r="A1" s="112" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="125"/>
-      <c r="C1" s="125"/>
-      <c r="D1" s="126"/>
+      <c r="B1" s="113"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="114"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="124" t="s">
+      <c r="F1" s="112" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="125"/>
-      <c r="H1" s="125"/>
-      <c r="I1" s="126"/>
+      <c r="G1" s="113"/>
+      <c r="H1" s="113"/>
+      <c r="I1" s="114"/>
     </row>
     <row r="2" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="89" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="92" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2" s="93">
         <v>1</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="94" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
+      <c r="G2" s="93"/>
+      <c r="H2" s="93"/>
+      <c r="I2" s="93"/>
     </row>
     <row r="3" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="89" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="90" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="91" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="92" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="93">
         <v>2</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="94" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
+      <c r="G3" s="93"/>
+      <c r="H3" s="93"/>
+      <c r="I3" s="93"/>
     </row>
     <row r="4" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A4" s="13"/>
-      <c r="B4" s="14"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="6">
+      <c r="A4" s="95"/>
+      <c r="B4" s="96"/>
+      <c r="C4" s="95"/>
+      <c r="D4" s="97" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="93">
         <v>3</v>
       </c>
-      <c r="F4" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
+      <c r="F4" s="98" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="93"/>
+      <c r="H4" s="93"/>
+      <c r="I4" s="93"/>
     </row>
     <row r="5" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A5" s="13"/>
-      <c r="B5" s="17" t="s">
+      <c r="A5" s="95"/>
+      <c r="B5" s="99" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="91" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="92" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="93">
         <v>4</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="94" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
+      <c r="G5" s="93"/>
+      <c r="H5" s="93"/>
+      <c r="I5" s="93"/>
     </row>
     <row r="6" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A6" s="13"/>
-      <c r="B6" s="17" t="s">
+      <c r="A6" s="95"/>
+      <c r="B6" s="99" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="91" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="92" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="93">
         <v>5</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="94" t="s">
         <v>20</v>
       </c>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
+      <c r="G6" s="93"/>
+      <c r="H6" s="93"/>
+      <c r="I6" s="93"/>
     </row>
     <row r="7" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="100" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="101" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="92" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="93">
         <v>6</v>
       </c>
-      <c r="F7" s="20" t="s">
+      <c r="F7" s="95" t="s">
         <v>23</v>
       </c>
-      <c r="G7" s="21" t="s">
+      <c r="G7" s="102" t="s">
         <v>24</v>
       </c>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
+      <c r="H7" s="93"/>
+      <c r="I7" s="93"/>
     </row>
     <row r="8" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="100" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="101" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="91" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D8" s="92" t="s">
         <v>26</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="93">
         <v>7</v>
       </c>
-      <c r="F8" s="22" t="s">
+      <c r="F8" s="103" t="s">
         <v>27</v>
       </c>
-      <c r="G8" s="21" t="s">
+      <c r="G8" s="102" t="s">
         <v>28</v>
       </c>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
+      <c r="H8" s="93"/>
+      <c r="I8" s="93"/>
     </row>
     <row r="9" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A9" s="13"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" s="6">
+      <c r="A9" s="95"/>
+      <c r="B9" s="93"/>
+      <c r="C9" s="95"/>
+      <c r="D9" s="97" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="93">
         <v>8</v>
       </c>
-      <c r="F9" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9" s="21" t="s">
+      <c r="F9" s="104" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="102" t="s">
         <v>29</v>
       </c>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
+      <c r="H9" s="93"/>
+      <c r="I9" s="93"/>
     </row>
     <row r="10" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A10" s="13"/>
-      <c r="B10" s="17" t="s">
+      <c r="A10" s="95"/>
+      <c r="B10" s="99" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="91" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="D10" s="92" t="s">
         <v>30</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="93">
         <v>9</v>
       </c>
-      <c r="F10" s="22" t="s">
+      <c r="F10" s="103" t="s">
         <v>31</v>
       </c>
-      <c r="G10" s="21" t="s">
+      <c r="G10" s="102" t="s">
         <v>32</v>
       </c>
-      <c r="H10" s="24" t="s">
+      <c r="H10" s="99" t="s">
         <v>17</v>
       </c>
-      <c r="I10" s="8"/>
+      <c r="I10" s="93"/>
     </row>
     <row r="11" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A11" s="13"/>
-      <c r="B11" s="17" t="s">
+      <c r="A11" s="95"/>
+      <c r="B11" s="99" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="91" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="92" t="s">
         <v>33</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="93">
         <v>10</v>
       </c>
-      <c r="F11" s="22" t="s">
+      <c r="F11" s="103" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="21" t="s">
+      <c r="G11" s="102" t="s">
         <v>35</v>
       </c>
-      <c r="H11" s="24" t="s">
+      <c r="H11" s="99" t="s">
         <v>13</v>
       </c>
-      <c r="I11" s="8"/>
+      <c r="I11" s="93"/>
     </row>
     <row r="12" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A12" s="18" t="s">
+      <c r="A12" s="100" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="99" t="s">
         <v>3</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="91" t="s">
         <v>36</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D12" s="92" t="s">
         <v>37</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="93">
         <v>11</v>
       </c>
-      <c r="F12" s="12" t="s">
+      <c r="F12" s="94" t="s">
         <v>38</v>
       </c>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
+      <c r="G12" s="93"/>
+      <c r="H12" s="93"/>
+      <c r="I12" s="93"/>
     </row>
     <row r="13" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A13" s="18" t="s">
+      <c r="A13" s="100" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="99" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="91" t="s">
         <v>39</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="D13" s="92" t="s">
         <v>40</v>
       </c>
-      <c r="E13" s="6">
-        <v>12</v>
-      </c>
-      <c r="F13" s="25" t="s">
+      <c r="E13" s="93">
+        <v>12</v>
+      </c>
+      <c r="F13" s="103" t="s">
         <v>41</v>
       </c>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
+      <c r="G13" s="93"/>
+      <c r="H13" s="93"/>
+      <c r="I13" s="93"/>
     </row>
     <row r="14" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A14" s="13"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" s="6">
+      <c r="A14" s="95"/>
+      <c r="B14" s="93"/>
+      <c r="C14" s="95"/>
+      <c r="D14" s="97" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" s="93">
         <v>13</v>
       </c>
-      <c r="F14" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
+      <c r="F14" s="104" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" s="93"/>
+      <c r="H14" s="93"/>
+      <c r="I14" s="93"/>
     </row>
     <row r="15" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A15" s="13"/>
-      <c r="B15" s="17" t="s">
+      <c r="A15" s="95"/>
+      <c r="B15" s="99" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="91" t="s">
         <v>42</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" s="92" t="s">
         <v>43</v>
       </c>
-      <c r="E15" s="6">
+      <c r="E15" s="93">
         <v>14</v>
       </c>
-      <c r="F15" s="25" t="s">
+      <c r="F15" s="103" t="s">
         <v>44</v>
       </c>
-      <c r="G15" s="8"/>
-      <c r="H15" s="17" t="s">
+      <c r="G15" s="93"/>
+      <c r="H15" s="99" t="s">
         <v>8</v>
       </c>
-      <c r="I15" s="8"/>
+      <c r="I15" s="93"/>
     </row>
     <row r="16" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A16" s="13"/>
-      <c r="B16" s="17" t="s">
+      <c r="A16" s="95"/>
+      <c r="B16" s="99" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="D16" s="27" t="s">
+      <c r="D16" s="103" t="s">
         <v>46</v>
       </c>
-      <c r="E16" s="6">
+      <c r="E16" s="93">
         <v>15</v>
       </c>
-      <c r="F16" s="25" t="s">
+      <c r="F16" s="103" t="s">
         <v>47</v>
       </c>
-      <c r="G16" s="8"/>
-      <c r="H16" s="17" t="s">
+      <c r="G16" s="93"/>
+      <c r="H16" s="99" t="s">
         <v>3</v>
       </c>
-      <c r="I16" s="8"/>
+      <c r="I16" s="93"/>
     </row>
     <row r="17" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A17" s="18" t="s">
+      <c r="A17" s="100" t="s">
         <v>2</v>
       </c>
-      <c r="B17" s="17" t="s">
+      <c r="B17" s="99" t="s">
         <v>3</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="91" t="s">
         <v>36</v>
       </c>
-      <c r="D17" s="27" t="s">
+      <c r="D17" s="103" t="s">
         <v>48</v>
       </c>
-      <c r="E17" s="6">
+      <c r="E17" s="93">
         <v>16</v>
       </c>
-      <c r="F17" s="25" t="s">
+      <c r="F17" s="103" t="s">
         <v>49</v>
       </c>
-      <c r="G17" s="28" t="s">
+      <c r="G17" s="105" t="s">
         <v>18</v>
       </c>
-      <c r="H17" s="17" t="s">
+      <c r="H17" s="99" t="s">
         <v>17</v>
       </c>
-      <c r="I17" s="8"/>
+      <c r="I17" s="93"/>
     </row>
     <row r="18" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A18" s="18" t="s">
+      <c r="A18" s="100" t="s">
         <v>7</v>
       </c>
-      <c r="B18" s="17" t="s">
+      <c r="B18" s="99" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="91" t="s">
         <v>39</v>
       </c>
-      <c r="D18" s="11" t="s">
+      <c r="D18" s="92" t="s">
         <v>50</v>
       </c>
-      <c r="E18" s="6">
+      <c r="E18" s="93">
         <v>17</v>
       </c>
-      <c r="F18" s="25" t="s">
+      <c r="F18" s="103" t="s">
         <v>51</v>
       </c>
-      <c r="G18" s="28" t="s">
+      <c r="G18" s="105" t="s">
         <v>14</v>
       </c>
-      <c r="H18" s="17" t="s">
+      <c r="H18" s="99" t="s">
         <v>52</v>
       </c>
-      <c r="I18" s="8"/>
+      <c r="I18" s="93"/>
     </row>
     <row r="19" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A19" s="13"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="E19" s="6">
+      <c r="A19" s="95"/>
+      <c r="B19" s="93"/>
+      <c r="C19" s="95"/>
+      <c r="D19" s="97" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" s="93">
         <v>18</v>
       </c>
-      <c r="F19" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="G19" s="8"/>
-      <c r="H19" s="29"/>
-      <c r="I19" s="8"/>
+      <c r="F19" s="104" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19" s="93"/>
+      <c r="H19" s="95"/>
+      <c r="I19" s="93"/>
     </row>
     <row r="20" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A20" s="13"/>
-      <c r="B20" s="17" t="s">
+      <c r="A20" s="95"/>
+      <c r="B20" s="99" t="s">
         <v>13</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C20" s="91" t="s">
         <v>53</v>
       </c>
-      <c r="D20" s="11" t="s">
+      <c r="D20" s="92" t="s">
         <v>54</v>
       </c>
-      <c r="E20" s="6">
+      <c r="E20" s="93">
         <v>19</v>
       </c>
-      <c r="F20" s="25" t="s">
+      <c r="F20" s="103" t="s">
         <v>55</v>
       </c>
-      <c r="G20" s="28" t="s">
+      <c r="G20" s="105" t="s">
         <v>9</v>
       </c>
-      <c r="H20" s="17" t="s">
+      <c r="H20" s="99" t="s">
         <v>8</v>
       </c>
-      <c r="I20" s="18" t="s">
+      <c r="I20" s="100" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A21" s="13"/>
-      <c r="B21" s="17" t="s">
+      <c r="A21" s="95"/>
+      <c r="B21" s="99" t="s">
         <v>17</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C21" s="91" t="s">
         <v>56</v>
       </c>
-      <c r="D21" s="11" t="s">
+      <c r="D21" s="92" t="s">
         <v>57</v>
       </c>
-      <c r="E21" s="6">
+      <c r="E21" s="93">
         <v>20</v>
       </c>
-      <c r="F21" s="25" t="s">
+      <c r="F21" s="103" t="s">
         <v>58</v>
       </c>
-      <c r="G21" s="28" t="s">
+      <c r="G21" s="105" t="s">
         <v>4</v>
       </c>
-      <c r="H21" s="17" t="s">
+      <c r="H21" s="99" t="s">
         <v>3</v>
       </c>
-      <c r="I21" s="18" t="s">
+      <c r="I21" s="100" t="s">
         <v>2</v>
       </c>
     </row>
@@ -4146,7 +4017,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1" gridLines="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup scale="140" pageOrder="overThenDown" orientation="landscape" cellComments="atEnd"/>
+  <pageSetup scale="140" pageOrder="overThenDown" orientation="landscape" cellComments="atEnd" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4164,364 +4035,364 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A1" s="124" t="s">
+      <c r="A1" s="118" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="125"/>
-      <c r="C1" s="125"/>
-      <c r="D1" s="126"/>
+      <c r="B1" s="119"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="120"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="118" t="s">
+      <c r="F1" s="112" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="120"/>
+      <c r="G1" s="113"/>
+      <c r="H1" s="113"/>
+      <c r="I1" s="114"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A2" s="30"/>
-      <c r="B2" s="30"/>
-      <c r="C2" s="31" t="s">
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="32" t="s">
+      <c r="D2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="33">
+      <c r="E2" s="7">
         <v>1</v>
       </c>
-      <c r="F2" s="34" t="s">
+      <c r="F2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="35"/>
+      <c r="G2" s="9"/>
     </row>
     <row r="3" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A3" s="30"/>
-      <c r="B3" s="30"/>
-      <c r="C3" s="31" t="s">
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="32" t="s">
+      <c r="D3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="33">
+      <c r="E3" s="7">
         <v>2</v>
       </c>
-      <c r="F3" s="34" t="s">
+      <c r="F3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="34" t="s">
+      <c r="G3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="L3" s="36"/>
+      <c r="L3" s="10"/>
     </row>
     <row r="4" spans="1:12" ht="15.75" customHeight="1">
-      <c r="C4" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="33">
+      <c r="C4" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="7">
         <v>3</v>
       </c>
-      <c r="F4" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="37" t="s">
+      <c r="F4" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="11" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="15.75" customHeight="1">
-      <c r="B5" s="30"/>
-      <c r="C5" s="114" t="s">
+      <c r="B5" s="4"/>
+      <c r="C5" s="106" t="s">
         <v>59</v>
       </c>
-      <c r="D5" s="32" t="s">
+      <c r="D5" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="33">
+      <c r="E5" s="7">
         <v>4</v>
       </c>
-      <c r="F5" s="34" t="s">
+      <c r="F5" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="35"/>
+      <c r="G5" s="9"/>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1">
-      <c r="B6" s="30"/>
-      <c r="C6" s="116"/>
-      <c r="D6" s="32" t="s">
+      <c r="B6" s="4"/>
+      <c r="C6" s="108"/>
+      <c r="D6" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="33">
+      <c r="E6" s="7">
         <v>5</v>
       </c>
-      <c r="F6" s="34" t="s">
+      <c r="F6" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="G6" s="34" t="s">
+      <c r="G6" s="8" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A7" s="30"/>
-      <c r="B7" s="30"/>
-      <c r="C7" s="116"/>
-      <c r="D7" s="32" t="s">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="108"/>
+      <c r="D7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="33">
+      <c r="E7" s="7">
         <v>6</v>
       </c>
-      <c r="F7" s="38" t="s">
+      <c r="F7" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="G7" s="35"/>
+      <c r="G7" s="9"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A8" s="30"/>
-      <c r="B8" s="30"/>
-      <c r="C8" s="115"/>
-      <c r="D8" s="32" t="s">
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="107"/>
+      <c r="D8" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E8" s="33">
+      <c r="E8" s="7">
         <v>7</v>
       </c>
-      <c r="F8" s="39" t="s">
+      <c r="F8" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="G8" s="38" t="s">
+      <c r="G8" s="12" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="15.75" customHeight="1">
-      <c r="C9" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" s="33">
+      <c r="C9" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="7">
         <v>8</v>
       </c>
-      <c r="F9" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9" s="37" t="s">
+      <c r="F9" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="11" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="15.75" customHeight="1">
-      <c r="B10" s="30"/>
-      <c r="C10" s="114" t="s">
+      <c r="B10" s="4"/>
+      <c r="C10" s="106" t="s">
         <v>60</v>
       </c>
-      <c r="D10" s="32" t="s">
+      <c r="D10" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="E10" s="33">
+      <c r="E10" s="7">
         <v>9</v>
       </c>
-      <c r="F10" s="39" t="s">
+      <c r="F10" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="G10" s="38" t="s">
+      <c r="G10" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="H10" s="30"/>
+      <c r="H10" s="4"/>
     </row>
     <row r="11" spans="1:12" ht="15.75" customHeight="1">
-      <c r="B11" s="30"/>
-      <c r="C11" s="116"/>
-      <c r="D11" s="32" t="s">
+      <c r="B11" s="4"/>
+      <c r="C11" s="108"/>
+      <c r="D11" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="E11" s="33">
+      <c r="E11" s="7">
         <v>10</v>
       </c>
-      <c r="F11" s="39" t="s">
+      <c r="F11" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="38" t="s">
+      <c r="G11" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="H11" s="30"/>
+      <c r="H11" s="4"/>
     </row>
     <row r="12" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A12" s="30"/>
-      <c r="B12" s="30"/>
-      <c r="C12" s="116"/>
-      <c r="D12" s="32" t="s">
+      <c r="A12" s="4"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="108"/>
+      <c r="D12" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="E12" s="33">
+      <c r="E12" s="7">
         <v>11</v>
       </c>
-      <c r="F12" s="34" t="s">
+      <c r="F12" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="G12" s="35"/>
+      <c r="G12" s="9"/>
     </row>
     <row r="13" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A13" s="30"/>
-      <c r="B13" s="30"/>
-      <c r="C13" s="115"/>
-      <c r="D13" s="32" t="s">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="107"/>
+      <c r="D13" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E13" s="33">
-        <v>12</v>
-      </c>
-      <c r="F13" s="39" t="s">
+      <c r="E13" s="7">
+        <v>12</v>
+      </c>
+      <c r="F13" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="G13" s="41"/>
+      <c r="G13" s="15"/>
     </row>
     <row r="14" spans="1:12" ht="15.75" customHeight="1">
-      <c r="C14" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" s="33">
+      <c r="C14" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" s="7">
         <v>13</v>
       </c>
-      <c r="F14" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="G14" s="37" t="s">
+      <c r="F14" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" s="11" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15.75" customHeight="1">
-      <c r="B15" s="30"/>
-      <c r="C15" s="114" t="s">
+      <c r="B15" s="4"/>
+      <c r="C15" s="106" t="s">
         <v>61</v>
       </c>
-      <c r="D15" s="32" t="s">
+      <c r="D15" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="E15" s="33">
+      <c r="E15" s="7">
         <v>14</v>
       </c>
-      <c r="F15" s="39" t="s">
+      <c r="F15" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="G15" s="114" t="s">
+      <c r="G15" s="106" t="s">
         <v>62</v>
       </c>
-      <c r="H15" s="30"/>
+      <c r="H15" s="4"/>
     </row>
     <row r="16" spans="1:12" ht="15.75" customHeight="1">
-      <c r="B16" s="30"/>
-      <c r="C16" s="116"/>
-      <c r="D16" s="39" t="s">
+      <c r="B16" s="4"/>
+      <c r="C16" s="108"/>
+      <c r="D16" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="E16" s="33">
+      <c r="E16" s="7">
         <v>15</v>
       </c>
-      <c r="F16" s="39" t="s">
+      <c r="F16" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="G16" s="115"/>
-      <c r="H16" s="30"/>
+      <c r="G16" s="107"/>
+      <c r="H16" s="4"/>
     </row>
     <row r="17" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A17" s="30"/>
-      <c r="B17" s="30"/>
-      <c r="C17" s="116"/>
-      <c r="D17" s="39" t="s">
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="108"/>
+      <c r="D17" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="E17" s="33">
+      <c r="E17" s="7">
         <v>16</v>
       </c>
-      <c r="F17" s="39" t="s">
+      <c r="F17" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="G17" s="42" t="s">
+      <c r="G17" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="H17" s="30"/>
+      <c r="H17" s="4"/>
     </row>
     <row r="18" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A18" s="30"/>
-      <c r="B18" s="30"/>
-      <c r="C18" s="115"/>
-      <c r="D18" s="32" t="s">
+      <c r="A18" s="4"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="107"/>
+      <c r="D18" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E18" s="33">
+      <c r="E18" s="7">
         <v>17</v>
       </c>
-      <c r="F18" s="39" t="s">
+      <c r="F18" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="G18" s="42" t="s">
+      <c r="G18" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="H18" s="30"/>
+      <c r="H18" s="4"/>
     </row>
     <row r="19" spans="1:9" ht="15.75" customHeight="1">
-      <c r="C19" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="D19" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="E19" s="33">
+      <c r="C19" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" s="7">
         <v>18</v>
       </c>
-      <c r="F19" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="G19" s="37" t="s">
+      <c r="F19" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19" s="11" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="15.75" customHeight="1">
-      <c r="B20" s="30"/>
-      <c r="C20" s="31" t="s">
+      <c r="B20" s="4"/>
+      <c r="C20" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D20" s="32" t="s">
+      <c r="D20" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="E20" s="33">
+      <c r="E20" s="7">
         <v>19</v>
       </c>
-      <c r="F20" s="39" t="s">
+      <c r="F20" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="G20" s="42" t="s">
+      <c r="G20" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="H20" s="30"/>
-      <c r="I20" s="30"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
     </row>
     <row r="21" spans="1:9" ht="15.75" customHeight="1">
-      <c r="B21" s="30"/>
-      <c r="C21" s="31" t="s">
+      <c r="B21" s="4"/>
+      <c r="C21" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D21" s="32" t="s">
+      <c r="D21" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E21" s="33">
+      <c r="E21" s="7">
         <v>20</v>
       </c>
-      <c r="F21" s="39" t="s">
+      <c r="F21" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="G21" s="42" t="s">
+      <c r="G21" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="H21" s="30"/>
-      <c r="I21" s="30"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -4552,442 +4423,442 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A1" s="118" t="s">
+      <c r="A1" s="112" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="120"/>
+      <c r="B1" s="113"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="114"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="118" t="s">
+      <c r="F1" s="112" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="120"/>
+      <c r="G1" s="113"/>
+      <c r="H1" s="113"/>
+      <c r="I1" s="114"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A2" s="114" t="s">
+      <c r="A2" s="106" t="s">
         <v>63</v>
       </c>
-      <c r="B2" s="43" t="s">
+      <c r="B2" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="C2" s="31" t="s">
+      <c r="C2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="32" t="s">
+      <c r="D2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="33">
+      <c r="E2" s="7">
         <v>1</v>
       </c>
-      <c r="F2" s="34" t="s">
+      <c r="F2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="35"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
     </row>
     <row r="3" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A3" s="115"/>
-      <c r="B3" s="43" t="s">
+      <c r="A3" s="107"/>
+      <c r="B3" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="C3" s="31" t="s">
+      <c r="C3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="32" t="s">
+      <c r="D3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="33">
+      <c r="E3" s="7">
         <v>2</v>
       </c>
-      <c r="F3" s="34" t="s">
+      <c r="F3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="34" t="s">
+      <c r="G3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="43" t="s">
+      <c r="H3" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="I3" s="114" t="s">
+      <c r="I3" s="106" t="s">
         <v>67</v>
       </c>
-      <c r="L3" s="36"/>
+      <c r="L3" s="10"/>
     </row>
     <row r="4" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="33">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="7">
         <v>3</v>
       </c>
-      <c r="F4" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="H4" s="43" t="s">
+      <c r="F4" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="I4" s="115"/>
+      <c r="I4" s="107"/>
     </row>
     <row r="5" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A5" s="43" t="s">
+      <c r="A5" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="B5" s="43" t="s">
+      <c r="B5" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="C5" s="114" t="s">
+      <c r="C5" s="106" t="s">
         <v>59</v>
       </c>
-      <c r="D5" s="32" t="s">
+      <c r="D5" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="33">
+      <c r="E5" s="7">
         <v>4</v>
       </c>
-      <c r="F5" s="34" t="s">
+      <c r="F5" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="35"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A6" s="43" t="s">
+      <c r="A6" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="B6" s="43" t="s">
+      <c r="B6" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="C6" s="116"/>
-      <c r="D6" s="32" t="s">
+      <c r="C6" s="108"/>
+      <c r="D6" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="33">
+      <c r="E6" s="7">
         <v>5</v>
       </c>
-      <c r="F6" s="34" t="s">
+      <c r="F6" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="G6" s="34" t="s">
+      <c r="G6" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="43" t="s">
+      <c r="H6" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="I6" s="43" t="s">
+      <c r="I6" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="J6" s="43" t="s">
+      <c r="J6" s="17" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="116"/>
-      <c r="D7" s="32" t="s">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="108"/>
+      <c r="D7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="33">
+      <c r="E7" s="7">
         <v>6</v>
       </c>
-      <c r="F7" s="38" t="s">
+      <c r="F7" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="G7" s="35"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="115"/>
-      <c r="D8" s="32" t="s">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="107"/>
+      <c r="D8" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E8" s="33">
+      <c r="E8" s="7">
         <v>7</v>
       </c>
-      <c r="F8" s="39" t="s">
+      <c r="F8" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="G8" s="38" t="s">
+      <c r="G8" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
     </row>
     <row r="9" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" s="33">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="7">
         <v>8</v>
       </c>
-      <c r="F9" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
+      <c r="F9" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
     </row>
     <row r="10" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A10" s="43" t="s">
+      <c r="A10" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="B10" s="43" t="s">
+      <c r="B10" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="C10" s="114" t="s">
+      <c r="C10" s="106" t="s">
         <v>60</v>
       </c>
-      <c r="D10" s="32" t="s">
+      <c r="D10" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="E10" s="33">
+      <c r="E10" s="7">
         <v>9</v>
       </c>
-      <c r="F10" s="39" t="s">
+      <c r="F10" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="G10" s="38" t="s">
+      <c r="G10" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
     </row>
     <row r="11" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="116"/>
-      <c r="D11" s="32" t="s">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="108"/>
+      <c r="D11" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="E11" s="33">
+      <c r="E11" s="7">
         <v>10</v>
       </c>
-      <c r="F11" s="39" t="s">
+      <c r="F11" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="38" t="s">
+      <c r="G11" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
     </row>
     <row r="12" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="116"/>
-      <c r="D12" s="32" t="s">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="108"/>
+      <c r="D12" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="E12" s="33">
+      <c r="E12" s="7">
         <v>11</v>
       </c>
-      <c r="F12" s="34" t="s">
+      <c r="F12" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="G12" s="35"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
     </row>
     <row r="13" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="115"/>
-      <c r="D13" s="32" t="s">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="107"/>
+      <c r="D13" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E13" s="33">
-        <v>12</v>
-      </c>
-      <c r="F13" s="39" t="s">
+      <c r="E13" s="7">
+        <v>12</v>
+      </c>
+      <c r="F13" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="G13" s="41"/>
-      <c r="H13" s="43" t="s">
+      <c r="G13" s="15"/>
+      <c r="H13" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="I13" s="43" t="s">
+      <c r="I13" s="17" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="15.75" customHeight="1">
-      <c r="C14" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" s="33">
+      <c r="C14" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" s="7">
         <v>13</v>
       </c>
-      <c r="F14" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="G14" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
+      <c r="F14" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
     </row>
     <row r="15" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A15" s="30"/>
-      <c r="B15" s="30"/>
-      <c r="C15" s="114" t="s">
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="106" t="s">
         <v>61</v>
       </c>
-      <c r="D15" s="32" t="s">
+      <c r="D15" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="E15" s="33">
+      <c r="E15" s="7">
         <v>14</v>
       </c>
-      <c r="F15" s="39" t="s">
+      <c r="F15" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="G15" s="114" t="s">
+      <c r="G15" s="106" t="s">
         <v>62</v>
       </c>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
     </row>
     <row r="16" spans="1:12" ht="15.75" customHeight="1">
-      <c r="B16" s="30"/>
-      <c r="C16" s="116"/>
-      <c r="D16" s="39" t="s">
+      <c r="B16" s="4"/>
+      <c r="C16" s="108"/>
+      <c r="D16" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="E16" s="33">
+      <c r="E16" s="7">
         <v>15</v>
       </c>
-      <c r="F16" s="39" t="s">
+      <c r="F16" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="G16" s="115"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
+      <c r="G16" s="107"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
     </row>
     <row r="17" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="116"/>
-      <c r="D17" s="39" t="s">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="108"/>
+      <c r="D17" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="E17" s="33">
+      <c r="E17" s="7">
         <v>16</v>
       </c>
-      <c r="F17" s="39" t="s">
+      <c r="F17" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="G17" s="42" t="s">
+      <c r="G17" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
     </row>
     <row r="18" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="115"/>
-      <c r="D18" s="32" t="s">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="107"/>
+      <c r="D18" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E18" s="33">
+      <c r="E18" s="7">
         <v>17</v>
       </c>
-      <c r="F18" s="39" t="s">
+      <c r="F18" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="G18" s="42" t="s">
+      <c r="G18" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
     </row>
     <row r="19" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="D19" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="E19" s="33">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" s="7">
         <v>18</v>
       </c>
-      <c r="F19" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="G19" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8"/>
+      <c r="F19" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
     </row>
     <row r="20" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="31" t="s">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D20" s="32" t="s">
+      <c r="D20" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="E20" s="33">
+      <c r="E20" s="7">
         <v>19</v>
       </c>
-      <c r="F20" s="39" t="s">
+      <c r="F20" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="G20" s="42" t="s">
+      <c r="G20" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="H20" s="8"/>
-      <c r="I20" s="8"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
     </row>
     <row r="21" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="31" t="s">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D21" s="32" t="s">
+      <c r="D21" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E21" s="33">
+      <c r="E21" s="7">
         <v>20</v>
       </c>
-      <c r="F21" s="39" t="s">
+      <c r="F21" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="G21" s="42" t="s">
+      <c r="G21" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="H21" s="8"/>
-      <c r="I21" s="8"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -5018,125 +4889,125 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="12.75">
-      <c r="A1" s="33"/>
-      <c r="B1" s="44" t="s">
+      <c r="A1" s="7"/>
+      <c r="B1" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="C1" s="44" t="s">
+      <c r="C1" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="D1" s="30"/>
+      <c r="D1" s="4"/>
     </row>
     <row r="2" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A2" s="33">
+      <c r="A2" s="7">
         <v>1</v>
       </c>
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="C2" s="45" t="s">
+      <c r="C2" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="D2" s="30"/>
+      <c r="D2" s="4"/>
     </row>
     <row r="3" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A3" s="33">
+      <c r="A3" s="7">
         <v>2</v>
       </c>
-      <c r="B3" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="30"/>
+      <c r="B3" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="4"/>
     </row>
     <row r="4" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A4" s="33">
+      <c r="A4" s="7">
         <v>3</v>
       </c>
-      <c r="B4" s="47" t="s">
+      <c r="B4" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="C4" s="47" t="s">
+      <c r="C4" s="21" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A5" s="33">
+      <c r="A5" s="7">
         <v>4</v>
       </c>
-      <c r="B5" s="47" t="s">
+      <c r="B5" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="C5" s="47" t="s">
+      <c r="C5" s="21" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A6" s="33">
+      <c r="A6" s="7">
         <v>5</v>
       </c>
-      <c r="B6" s="48" t="s">
+      <c r="B6" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="C6" s="49"/>
-      <c r="D6" s="30"/>
+      <c r="C6" s="23"/>
+      <c r="D6" s="4"/>
     </row>
     <row r="7" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A7" s="33">
+      <c r="A7" s="7">
         <v>6</v>
       </c>
-      <c r="B7" s="48" t="s">
+      <c r="B7" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="C7" s="49"/>
-      <c r="D7" s="30"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="4"/>
     </row>
     <row r="8" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A8" s="33">
+      <c r="A8" s="7">
         <v>7</v>
       </c>
-      <c r="B8" s="50" t="s">
+      <c r="B8" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="C8" s="50" t="s">
+      <c r="C8" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="D8" s="30" t="s">
+      <c r="D8" s="4" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A9" s="33">
+      <c r="A9" s="7">
         <v>8</v>
       </c>
-      <c r="B9" s="50" t="s">
+      <c r="B9" s="24" t="s">
         <v>88</v>
       </c>
-      <c r="C9" s="50" t="s">
+      <c r="C9" s="24" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A10" s="33">
+      <c r="A10" s="7">
         <v>9</v>
       </c>
-      <c r="B10" s="50" t="s">
+      <c r="B10" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="C10" s="50" t="s">
+      <c r="C10" s="24" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A11" s="33">
+      <c r="A11" s="7">
         <v>10</v>
       </c>
-      <c r="B11" s="50" t="s">
+      <c r="B11" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="C11" s="50" t="s">
+      <c r="C11" s="24" t="s">
         <v>93</v>
       </c>
     </row>
@@ -5159,437 +5030,437 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A1" s="118" t="s">
+      <c r="A1" s="112" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="120"/>
+      <c r="B1" s="113"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="114"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="118" t="s">
+      <c r="F1" s="112" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="120"/>
+      <c r="G1" s="113"/>
+      <c r="H1" s="113"/>
+      <c r="I1" s="114"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A2" s="54"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="53" t="s">
+      <c r="A2" s="28"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="32" t="s">
+      <c r="D2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="33">
+      <c r="E2" s="7">
         <v>1</v>
       </c>
-      <c r="F2" s="34" t="s">
+      <c r="F2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="35"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
     </row>
     <row r="3" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A3" s="106"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="53" t="s">
+      <c r="A3" s="80"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="32" t="s">
+      <c r="D3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="33">
+      <c r="E3" s="7">
         <v>2</v>
       </c>
-      <c r="F3" s="34" t="s">
+      <c r="F3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="34" t="s">
+      <c r="G3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="43" t="s">
+      <c r="H3" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="I3" s="114" t="s">
+      <c r="I3" s="106" t="s">
         <v>67</v>
       </c>
-      <c r="L3" s="36"/>
+      <c r="L3" s="10"/>
     </row>
     <row r="4" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="33">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="7">
         <v>3</v>
       </c>
-      <c r="F4" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="H4" s="43" t="s">
+      <c r="F4" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="I4" s="115"/>
+      <c r="I4" s="107"/>
     </row>
     <row r="5" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A5" s="107" t="s">
+      <c r="A5" s="81" t="s">
         <v>69</v>
       </c>
-      <c r="B5" s="107" t="s">
+      <c r="B5" s="81" t="s">
         <v>70</v>
       </c>
-      <c r="C5" s="132" t="s">
+      <c r="C5" s="110" t="s">
         <v>59</v>
       </c>
-      <c r="D5" s="32" t="s">
+      <c r="D5" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="33">
+      <c r="E5" s="7">
         <v>4</v>
       </c>
-      <c r="F5" s="34" t="s">
+      <c r="F5" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="35"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="133"/>
-      <c r="D6" s="32" t="s">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="111"/>
+      <c r="D6" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="33">
+      <c r="E6" s="7">
         <v>5</v>
       </c>
-      <c r="F6" s="34" t="s">
+      <c r="F6" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="G6" s="34" t="s">
+      <c r="G6" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="108" t="s">
+      <c r="H6" s="82" t="s">
         <v>72</v>
       </c>
-      <c r="I6" s="107" t="s">
+      <c r="I6" s="81" t="s">
         <v>73</v>
       </c>
-      <c r="J6" s="8"/>
+      <c r="J6" s="2"/>
     </row>
     <row r="7" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="116"/>
-      <c r="D7" s="32" t="s">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="108"/>
+      <c r="D7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="33">
+      <c r="E7" s="7">
         <v>6</v>
       </c>
-      <c r="F7" s="38" t="s">
+      <c r="F7" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="G7" s="35"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="115"/>
-      <c r="D8" s="32" t="s">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="107"/>
+      <c r="D8" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E8" s="33">
+      <c r="E8" s="7">
         <v>7</v>
       </c>
-      <c r="F8" s="39" t="s">
+      <c r="F8" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="G8" s="38" t="s">
+      <c r="G8" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
     </row>
     <row r="9" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" s="33">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="7">
         <v>8</v>
       </c>
-      <c r="F9" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
+      <c r="F9" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
     </row>
     <row r="10" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A10" s="43" t="s">
+      <c r="A10" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="B10" s="43" t="s">
+      <c r="B10" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="C10" s="114" t="s">
+      <c r="C10" s="106" t="s">
         <v>60</v>
       </c>
-      <c r="D10" s="32" t="s">
+      <c r="D10" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="E10" s="33">
+      <c r="E10" s="7">
         <v>9</v>
       </c>
-      <c r="F10" s="39" t="s">
+      <c r="F10" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="G10" s="51" t="s">
+      <c r="G10" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="H10" s="95" t="s">
+      <c r="H10" s="69" t="s">
         <v>220</v>
       </c>
-      <c r="I10" s="130" t="s">
+      <c r="I10" s="124" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="116"/>
-      <c r="D11" s="32" t="s">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="108"/>
+      <c r="D11" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="E11" s="33">
+      <c r="E11" s="7">
         <v>10</v>
       </c>
-      <c r="F11" s="39" t="s">
+      <c r="F11" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="51" t="s">
+      <c r="G11" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="H11" s="95" t="s">
+      <c r="H11" s="69" t="s">
         <v>219</v>
       </c>
-      <c r="I11" s="131"/>
+      <c r="I11" s="125"/>
     </row>
     <row r="12" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="116"/>
-      <c r="D12" s="32" t="s">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="108"/>
+      <c r="D12" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="E12" s="33">
+      <c r="E12" s="7">
         <v>11</v>
       </c>
-      <c r="F12" s="34" t="s">
+      <c r="F12" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="G12" s="35"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
     </row>
     <row r="13" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="115"/>
-      <c r="D13" s="32" t="s">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="107"/>
+      <c r="D13" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E13" s="33">
-        <v>12</v>
-      </c>
-      <c r="F13" s="39" t="s">
+      <c r="E13" s="7">
+        <v>12</v>
+      </c>
+      <c r="F13" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="G13" s="41"/>
-      <c r="H13" s="43" t="s">
+      <c r="G13" s="15"/>
+      <c r="H13" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="I13" s="43" t="s">
+      <c r="I13" s="17" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="15.75" customHeight="1">
-      <c r="C14" s="109" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" s="33">
+      <c r="C14" s="83" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" s="7">
         <v>13</v>
       </c>
-      <c r="F14" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="G14" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
+      <c r="F14" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
     </row>
     <row r="15" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A15" s="54"/>
-      <c r="B15" s="30"/>
-      <c r="C15" s="127" t="s">
+      <c r="A15" s="28"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="121" t="s">
         <v>61</v>
       </c>
-      <c r="D15" s="32" t="s">
+      <c r="D15" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="E15" s="33">
+      <c r="E15" s="7">
         <v>14</v>
       </c>
-      <c r="F15" s="39" t="s">
+      <c r="F15" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="G15" s="114" t="s">
+      <c r="G15" s="106" t="s">
         <v>62</v>
       </c>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
     </row>
     <row r="16" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A16" s="54"/>
-      <c r="B16" s="30"/>
-      <c r="C16" s="128"/>
-      <c r="D16" s="39" t="s">
+      <c r="A16" s="28"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="122"/>
+      <c r="D16" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="E16" s="33">
+      <c r="E16" s="7">
         <v>15</v>
       </c>
-      <c r="F16" s="39" t="s">
+      <c r="F16" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="G16" s="115"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
+      <c r="G16" s="107"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
     </row>
     <row r="17" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="128"/>
-      <c r="D17" s="39" t="s">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="122"/>
+      <c r="D17" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="E17" s="33">
+      <c r="E17" s="7">
         <v>16</v>
       </c>
-      <c r="F17" s="39" t="s">
+      <c r="F17" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="G17" s="42" t="s">
+      <c r="G17" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
     </row>
     <row r="18" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="129"/>
-      <c r="D18" s="32" t="s">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="123"/>
+      <c r="D18" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E18" s="33">
+      <c r="E18" s="7">
         <v>17</v>
       </c>
-      <c r="F18" s="39" t="s">
+      <c r="F18" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="G18" s="42" t="s">
+      <c r="G18" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
     </row>
     <row r="19" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="D19" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="E19" s="33">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" s="7">
         <v>18</v>
       </c>
-      <c r="F19" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="G19" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8"/>
+      <c r="F19" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
     </row>
     <row r="20" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="31" t="s">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D20" s="32" t="s">
+      <c r="D20" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="E20" s="33">
+      <c r="E20" s="7">
         <v>19</v>
       </c>
-      <c r="F20" s="39" t="s">
+      <c r="F20" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="G20" s="42" t="s">
+      <c r="G20" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="H20" s="8"/>
-      <c r="I20" s="8"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
     </row>
     <row r="21" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="31" t="s">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D21" s="32" t="s">
+      <c r="D21" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E21" s="33">
+      <c r="E21" s="7">
         <v>20</v>
       </c>
-      <c r="F21" s="39" t="s">
+      <c r="F21" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="G21" s="42" t="s">
+      <c r="G21" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="H21" s="8"/>
-      <c r="I21" s="8"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -5622,481 +5493,481 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A1" s="118" t="s">
+      <c r="A1" s="112" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="120"/>
+      <c r="B1" s="113"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="114"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="118" t="s">
+      <c r="F1" s="112" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="120"/>
+      <c r="G1" s="113"/>
+      <c r="H1" s="113"/>
+      <c r="I1" s="114"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A2" s="114" t="s">
+      <c r="A2" s="106" t="s">
         <v>94</v>
       </c>
-      <c r="B2" s="43" t="s">
+      <c r="B2" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="C2" s="31" t="s">
+      <c r="C2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="32" t="s">
+      <c r="D2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="33">
+      <c r="E2" s="7">
         <v>1</v>
       </c>
-      <c r="F2" s="34" t="s">
+      <c r="F2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="35"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
     </row>
     <row r="3" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A3" s="115"/>
-      <c r="B3" s="43" t="s">
+      <c r="A3" s="107"/>
+      <c r="B3" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="C3" s="31" t="s">
+      <c r="C3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="32" t="s">
+      <c r="D3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="33">
+      <c r="E3" s="7">
         <v>2</v>
       </c>
-      <c r="F3" s="34" t="s">
+      <c r="F3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="35"/>
-      <c r="H3" s="43" t="s">
+      <c r="G3" s="9"/>
+      <c r="H3" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="I3" s="114" t="s">
+      <c r="I3" s="106" t="s">
         <v>67</v>
       </c>
-      <c r="L3" s="36"/>
+      <c r="L3" s="10"/>
     </row>
     <row r="4" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="33">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="7">
         <v>3</v>
       </c>
-      <c r="F4" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="H4" s="43" t="s">
+      <c r="F4" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="I4" s="115"/>
+      <c r="I4" s="107"/>
     </row>
     <row r="5" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A5" s="114" t="s">
+      <c r="A5" s="106" t="s">
         <v>95</v>
       </c>
-      <c r="B5" s="43" t="s">
+      <c r="B5" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="C5" s="114" t="s">
+      <c r="C5" s="106" t="s">
         <v>59</v>
       </c>
-      <c r="D5" s="32" t="s">
+      <c r="D5" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="33">
+      <c r="E5" s="7">
         <v>4</v>
       </c>
-      <c r="F5" s="34" t="s">
+      <c r="F5" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="35"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A6" s="116"/>
-      <c r="B6" s="43" t="s">
+      <c r="A6" s="108"/>
+      <c r="B6" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="C6" s="116"/>
-      <c r="D6" s="32" t="s">
+      <c r="C6" s="108"/>
+      <c r="D6" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="33">
+      <c r="E6" s="7">
         <v>5</v>
       </c>
-      <c r="F6" s="34" t="s">
+      <c r="F6" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="G6" s="34" t="s">
+      <c r="G6" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="43" t="s">
+      <c r="H6" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="I6" s="43" t="s">
+      <c r="I6" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="J6" s="43" t="s">
+      <c r="J6" s="17" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A7" s="115"/>
-      <c r="B7" s="43" t="s">
+      <c r="A7" s="107"/>
+      <c r="B7" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="C7" s="116"/>
-      <c r="D7" s="32" t="s">
+      <c r="C7" s="108"/>
+      <c r="D7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="33">
+      <c r="E7" s="7">
         <v>6</v>
       </c>
-      <c r="F7" s="38" t="s">
+      <c r="F7" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="G7" s="35"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="115"/>
-      <c r="D8" s="32" t="s">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="107"/>
+      <c r="D8" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E8" s="33">
+      <c r="E8" s="7">
         <v>7</v>
       </c>
-      <c r="F8" s="39" t="s">
+      <c r="F8" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="G8" s="51" t="s">
+      <c r="G8" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
     </row>
     <row r="9" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" s="33">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="7">
         <v>8</v>
       </c>
-      <c r="F9" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9" s="52" t="s">
-        <v>12</v>
-      </c>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
+      <c r="F9" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
     </row>
     <row r="10" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A10" s="114" t="s">
+      <c r="A10" s="106" t="s">
         <v>98</v>
       </c>
-      <c r="B10" s="43" t="s">
+      <c r="B10" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="C10" s="114" t="s">
+      <c r="C10" s="106" t="s">
         <v>60</v>
       </c>
-      <c r="D10" s="32" t="s">
+      <c r="D10" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="E10" s="33">
+      <c r="E10" s="7">
         <v>9</v>
       </c>
-      <c r="F10" s="39" t="s">
+      <c r="F10" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="G10" s="51" t="s">
+      <c r="G10" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
     </row>
     <row r="11" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A11" s="116"/>
-      <c r="B11" s="43" t="s">
+      <c r="A11" s="108"/>
+      <c r="B11" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="C11" s="116"/>
-      <c r="D11" s="32" t="s">
+      <c r="C11" s="108"/>
+      <c r="D11" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="E11" s="33">
+      <c r="E11" s="7">
         <v>10</v>
       </c>
-      <c r="F11" s="39" t="s">
+      <c r="F11" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="51" t="s">
+      <c r="G11" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
     </row>
     <row r="12" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A12" s="115"/>
-      <c r="B12" s="43" t="s">
+      <c r="A12" s="107"/>
+      <c r="B12" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="C12" s="116"/>
-      <c r="D12" s="32" t="s">
+      <c r="C12" s="108"/>
+      <c r="D12" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="E12" s="33">
+      <c r="E12" s="7">
         <v>11</v>
       </c>
-      <c r="F12" s="34" t="s">
+      <c r="F12" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="G12" s="35"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
     </row>
     <row r="13" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A13" s="43" t="s">
+      <c r="A13" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="B13" s="43" t="s">
+      <c r="B13" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="C13" s="115"/>
-      <c r="D13" s="32" t="s">
+      <c r="C13" s="107"/>
+      <c r="D13" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E13" s="33">
-        <v>12</v>
-      </c>
-      <c r="F13" s="39" t="s">
+      <c r="E13" s="7">
+        <v>12</v>
+      </c>
+      <c r="F13" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="G13" s="41"/>
-      <c r="H13" s="43" t="s">
+      <c r="G13" s="15"/>
+      <c r="H13" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="I13" s="43" t="s">
+      <c r="I13" s="17" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" s="33">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" s="7">
         <v>13</v>
       </c>
-      <c r="F14" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="G14" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
+      <c r="F14" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
     </row>
     <row r="15" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A15" s="114" t="s">
+      <c r="A15" s="106" t="s">
         <v>102</v>
       </c>
-      <c r="B15" s="43" t="s">
+      <c r="B15" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="C15" s="114" t="s">
+      <c r="C15" s="106" t="s">
         <v>61</v>
       </c>
-      <c r="D15" s="32" t="s">
+      <c r="D15" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="E15" s="33">
+      <c r="E15" s="7">
         <v>14</v>
       </c>
-      <c r="F15" s="39" t="s">
+      <c r="F15" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="G15" s="114" t="s">
+      <c r="G15" s="106" t="s">
         <v>62</v>
       </c>
-      <c r="H15" s="43" t="s">
+      <c r="H15" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="I15" s="134" t="s">
+      <c r="I15" s="126" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A16" s="115"/>
-      <c r="B16" s="43" t="s">
+      <c r="A16" s="107"/>
+      <c r="B16" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="C16" s="116"/>
-      <c r="D16" s="39" t="s">
+      <c r="C16" s="108"/>
+      <c r="D16" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="E16" s="33">
+      <c r="E16" s="7">
         <v>15</v>
       </c>
-      <c r="F16" s="39" t="s">
+      <c r="F16" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="G16" s="115"/>
-      <c r="H16" s="43" t="s">
+      <c r="G16" s="107"/>
+      <c r="H16" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="I16" s="115"/>
+      <c r="I16" s="107"/>
     </row>
     <row r="17" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A17" s="114" t="s">
+      <c r="A17" s="106" t="s">
         <v>102</v>
       </c>
-      <c r="B17" s="43" t="s">
+      <c r="B17" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="C17" s="116"/>
-      <c r="D17" s="39" t="s">
+      <c r="C17" s="108"/>
+      <c r="D17" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="E17" s="33">
+      <c r="E17" s="7">
         <v>16</v>
       </c>
-      <c r="F17" s="39" t="s">
+      <c r="F17" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="G17" s="42" t="s">
+      <c r="G17" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="H17" s="43" t="s">
+      <c r="H17" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="I17" s="114" t="s">
+      <c r="I17" s="106" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A18" s="115"/>
-      <c r="B18" s="43" t="s">
+      <c r="A18" s="107"/>
+      <c r="B18" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="C18" s="115"/>
-      <c r="D18" s="32" t="s">
+      <c r="C18" s="107"/>
+      <c r="D18" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E18" s="33">
+      <c r="E18" s="7">
         <v>17</v>
       </c>
-      <c r="F18" s="39" t="s">
+      <c r="F18" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="G18" s="42" t="s">
+      <c r="G18" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="H18" s="43" t="s">
+      <c r="H18" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="I18" s="115"/>
+      <c r="I18" s="107"/>
     </row>
     <row r="19" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="D19" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="E19" s="33">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" s="7">
         <v>18</v>
       </c>
-      <c r="F19" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="G19" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8"/>
+      <c r="F19" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
     </row>
     <row r="20" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="53" t="s">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="D20" s="32" t="s">
+      <c r="D20" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="E20" s="33">
+      <c r="E20" s="7">
         <v>19</v>
       </c>
-      <c r="F20" s="39" t="s">
+      <c r="F20" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="G20" s="42" t="s">
+      <c r="G20" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="H20" s="43" t="s">
+      <c r="H20" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="I20" s="43" t="s">
+      <c r="I20" s="17" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="53" t="s">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="D21" s="32" t="s">
+      <c r="D21" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E21" s="33">
+      <c r="E21" s="7">
         <v>20</v>
       </c>
-      <c r="F21" s="39" t="s">
+      <c r="F21" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="G21" s="42" t="s">
+      <c r="G21" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="H21" s="43" t="s">
+      <c r="H21" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="I21" s="43" t="s">
+      <c r="I21" s="17" t="s">
         <v>112</v>
       </c>
     </row>
@@ -6142,586 +6013,586 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A1" s="118" t="s">
+      <c r="A1" s="112" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="120"/>
+      <c r="B1" s="113"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="114"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="118" t="s">
+      <c r="F1" s="112" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="120"/>
+      <c r="G1" s="113"/>
+      <c r="H1" s="113"/>
+      <c r="I1" s="114"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A2" s="121" t="s">
+      <c r="A2" s="115" t="s">
         <v>190</v>
       </c>
-      <c r="B2" s="88" t="s">
+      <c r="B2" s="62" t="s">
         <v>64</v>
       </c>
-      <c r="C2" s="53" t="s">
+      <c r="C2" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="32" t="s">
+      <c r="D2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="33">
+      <c r="E2" s="7">
         <v>1</v>
       </c>
-      <c r="F2" s="34" t="s">
+      <c r="F2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="35"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
     </row>
     <row r="3" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A3" s="122"/>
-      <c r="B3" s="88" t="s">
+      <c r="A3" s="116"/>
+      <c r="B3" s="62" t="s">
         <v>65</v>
       </c>
-      <c r="C3" s="53" t="s">
+      <c r="C3" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="32" t="s">
+      <c r="D3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="33">
+      <c r="E3" s="7">
         <v>2</v>
       </c>
-      <c r="F3" s="34" t="s">
+      <c r="F3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="35"/>
-      <c r="H3" s="43" t="s">
+      <c r="G3" s="9"/>
+      <c r="H3" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="I3" s="123" t="s">
+      <c r="I3" s="117" t="s">
         <v>192</v>
       </c>
-      <c r="L3" s="36"/>
+      <c r="L3" s="10"/>
     </row>
     <row r="4" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="33">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="7">
         <v>3</v>
       </c>
-      <c r="F4" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="H4" s="43" t="s">
+      <c r="F4" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="I4" s="115"/>
+      <c r="I4" s="107"/>
     </row>
     <row r="5" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A5" s="30"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="114" t="s">
+      <c r="A5" s="4"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="106" t="s">
         <v>59</v>
       </c>
-      <c r="D5" s="32" t="s">
+      <c r="D5" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="33">
+      <c r="E5" s="7">
         <v>4</v>
       </c>
-      <c r="F5" s="34" t="s">
+      <c r="F5" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="35"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A6" s="30"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="116"/>
-      <c r="D6" s="32" t="s">
+      <c r="A6" s="4"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="108"/>
+      <c r="D6" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="33">
+      <c r="E6" s="7">
         <v>5</v>
       </c>
-      <c r="F6" s="34" t="s">
+      <c r="F6" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="G6" s="34" t="s">
+      <c r="G6" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="43" t="s">
+      <c r="H6" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="I6" s="43" t="s">
+      <c r="I6" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="J6" s="43" t="s">
+      <c r="J6" s="17" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A7" s="30"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="116"/>
-      <c r="D7" s="32" t="s">
+      <c r="A7" s="4"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="108"/>
+      <c r="D7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="33">
+      <c r="E7" s="7">
         <v>6</v>
       </c>
-      <c r="F7" s="38" t="s">
+      <c r="F7" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="G7" s="35"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="115"/>
-      <c r="D8" s="32" t="s">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="107"/>
+      <c r="D8" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E8" s="33">
+      <c r="E8" s="7">
         <v>7</v>
       </c>
-      <c r="F8" s="39" t="s">
+      <c r="F8" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="G8" s="38" t="s">
+      <c r="G8" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
     </row>
     <row r="9" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" s="33">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="7">
         <v>8</v>
       </c>
-      <c r="F9" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
+      <c r="F9" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
     </row>
     <row r="10" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A10" s="43" t="s">
+      <c r="A10" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="B10" s="89" t="s">
+      <c r="B10" s="63" t="s">
         <v>193</v>
       </c>
-      <c r="C10" s="114" t="s">
+      <c r="C10" s="106" t="s">
         <v>60</v>
       </c>
-      <c r="D10" s="32" t="s">
+      <c r="D10" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="E10" s="33">
+      <c r="E10" s="7">
         <v>9</v>
       </c>
-      <c r="F10" s="39" t="s">
+      <c r="F10" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="G10" s="38" t="s">
+      <c r="G10" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
     </row>
     <row r="11" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A11" s="54"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="116"/>
-      <c r="D11" s="32" t="s">
+      <c r="A11" s="28"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="108"/>
+      <c r="D11" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="E11" s="33">
+      <c r="E11" s="7">
         <v>10</v>
       </c>
-      <c r="F11" s="39" t="s">
+      <c r="F11" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="38" t="s">
+      <c r="G11" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
     </row>
     <row r="12" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A12" s="54"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="116"/>
-      <c r="D12" s="32" t="s">
+      <c r="A12" s="28"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="108"/>
+      <c r="D12" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="E12" s="33">
+      <c r="E12" s="7">
         <v>11</v>
       </c>
-      <c r="F12" s="34" t="s">
+      <c r="F12" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="G12" s="35"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
     </row>
     <row r="13" spans="1:12" ht="15.75" customHeight="1">
-      <c r="C13" s="115"/>
-      <c r="D13" s="32" t="s">
+      <c r="C13" s="107"/>
+      <c r="D13" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E13" s="33">
-        <v>12</v>
-      </c>
-      <c r="F13" s="39" t="s">
+      <c r="E13" s="7">
+        <v>12</v>
+      </c>
+      <c r="F13" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="G13" s="41"/>
-      <c r="H13" s="43" t="s">
+      <c r="G13" s="15"/>
+      <c r="H13" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="I13" s="43" t="s">
+      <c r="I13" s="17" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" s="33">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" s="7">
         <v>13</v>
       </c>
-      <c r="F14" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="G14" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
+      <c r="F14" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
     </row>
     <row r="15" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A15" s="114" t="s">
+      <c r="A15" s="106" t="s">
         <v>102</v>
       </c>
-      <c r="B15" s="43" t="s">
+      <c r="B15" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="C15" s="114" t="s">
+      <c r="C15" s="106" t="s">
         <v>61</v>
       </c>
-      <c r="D15" s="32" t="s">
+      <c r="D15" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="E15" s="33">
+      <c r="E15" s="7">
         <v>14</v>
       </c>
-      <c r="F15" s="39" t="s">
+      <c r="F15" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="G15" s="114" t="s">
+      <c r="G15" s="106" t="s">
         <v>62</v>
       </c>
-      <c r="H15" s="43" t="s">
+      <c r="H15" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="I15" s="114" t="s">
+      <c r="I15" s="106" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A16" s="115"/>
-      <c r="B16" s="43" t="s">
+      <c r="A16" s="107"/>
+      <c r="B16" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="C16" s="116"/>
-      <c r="D16" s="39" t="s">
+      <c r="C16" s="108"/>
+      <c r="D16" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="E16" s="33">
+      <c r="E16" s="7">
         <v>15</v>
       </c>
-      <c r="F16" s="39" t="s">
+      <c r="F16" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="G16" s="115"/>
-      <c r="H16" s="43" t="s">
+      <c r="G16" s="107"/>
+      <c r="H16" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="I16" s="117"/>
+      <c r="I16" s="109"/>
     </row>
     <row r="17" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A17" s="114" t="s">
+      <c r="A17" s="106" t="s">
         <v>102</v>
       </c>
-      <c r="B17" s="43" t="s">
+      <c r="B17" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="C17" s="116"/>
-      <c r="D17" s="39" t="s">
+      <c r="C17" s="108"/>
+      <c r="D17" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="E17" s="33">
+      <c r="E17" s="7">
         <v>16</v>
       </c>
-      <c r="F17" s="39" t="s">
+      <c r="F17" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="G17" s="42" t="s">
+      <c r="G17" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="H17" s="8"/>
-      <c r="I17" s="54"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="28"/>
     </row>
     <row r="18" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A18" s="115"/>
-      <c r="B18" s="43" t="s">
+      <c r="A18" s="107"/>
+      <c r="B18" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="C18" s="115"/>
-      <c r="D18" s="32" t="s">
+      <c r="C18" s="107"/>
+      <c r="D18" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E18" s="33">
+      <c r="E18" s="7">
         <v>17</v>
       </c>
-      <c r="F18" s="39" t="s">
+      <c r="F18" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="G18" s="42" t="s">
+      <c r="G18" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="H18" s="8"/>
-      <c r="I18" s="54"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="28"/>
     </row>
     <row r="19" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="D19" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="E19" s="33">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" s="7">
         <v>18</v>
       </c>
-      <c r="F19" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="G19" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8"/>
+      <c r="F19" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
     </row>
     <row r="20" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="31" t="s">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D20" s="32" t="s">
+      <c r="D20" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="E20" s="33">
+      <c r="E20" s="7">
         <v>19</v>
       </c>
-      <c r="F20" s="39" t="s">
+      <c r="F20" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="G20" s="42" t="s">
+      <c r="G20" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="H20" s="43" t="s">
+      <c r="H20" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="I20" s="43" t="s">
+      <c r="I20" s="17" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="31" t="s">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D21" s="32" t="s">
+      <c r="D21" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E21" s="33">
+      <c r="E21" s="7">
         <v>20</v>
       </c>
-      <c r="F21" s="39" t="s">
+      <c r="F21" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="G21" s="42" t="s">
+      <c r="G21" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="H21" s="43" t="s">
+      <c r="H21" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="I21" s="43" t="s">
+      <c r="I21" s="17" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="12.75">
-      <c r="C23" s="44" t="s">
+      <c r="C23" s="18" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="12.75">
-      <c r="C24" s="55"/>
-      <c r="D24" s="37" t="s">
+      <c r="C24" s="29"/>
+      <c r="D24" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="E24" s="33"/>
-      <c r="F24" s="37" t="s">
+      <c r="E24" s="7"/>
+      <c r="F24" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="G24" s="56"/>
-      <c r="H24" s="46" t="s">
+      <c r="G24" s="30"/>
+      <c r="H24" s="20" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="12.75">
-      <c r="C25" s="57"/>
-      <c r="D25" s="58" t="s">
+      <c r="C25" s="31"/>
+      <c r="D25" s="32" t="s">
         <v>117</v>
       </c>
-      <c r="E25" s="33">
+      <c r="E25" s="7">
         <v>1</v>
       </c>
-      <c r="F25" s="59" t="s">
+      <c r="F25" s="33" t="s">
         <v>118</v>
       </c>
-      <c r="G25" s="60" t="s">
+      <c r="G25" s="34" t="s">
         <v>119</v>
       </c>
-      <c r="H25" s="50" t="s">
+      <c r="H25" s="24" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="12.75">
-      <c r="C26" s="61" t="s">
+      <c r="C26" s="35" t="s">
         <v>121</v>
       </c>
-      <c r="D26" s="61" t="s">
+      <c r="D26" s="35" t="s">
         <v>122</v>
       </c>
-      <c r="E26" s="33">
+      <c r="E26" s="7">
         <v>2</v>
       </c>
-      <c r="F26" s="59" t="s">
+      <c r="F26" s="33" t="s">
         <v>123</v>
       </c>
-      <c r="G26" s="60" t="s">
+      <c r="G26" s="34" t="s">
         <v>124</v>
       </c>
-      <c r="H26" s="50" t="s">
+      <c r="H26" s="24" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="12.75">
-      <c r="C27" s="61" t="s">
+      <c r="C27" s="35" t="s">
         <v>126</v>
       </c>
-      <c r="D27" s="61" t="s">
+      <c r="D27" s="35" t="s">
         <v>127</v>
       </c>
-      <c r="E27" s="33">
+      <c r="E27" s="7">
         <v>3</v>
       </c>
-      <c r="F27" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="G27" s="62"/>
-      <c r="H27" s="49"/>
+      <c r="F27" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G27" s="36"/>
+      <c r="H27" s="23"/>
     </row>
     <row r="28" spans="1:9" ht="12.75">
-      <c r="C28" s="61" t="s">
+      <c r="C28" s="35" t="s">
         <v>128</v>
       </c>
-      <c r="D28" s="61" t="s">
+      <c r="D28" s="35" t="s">
         <v>129</v>
       </c>
-      <c r="E28" s="33">
+      <c r="E28" s="7">
         <v>4</v>
       </c>
-      <c r="F28" s="63" t="s">
+      <c r="F28" s="37" t="s">
         <v>79</v>
       </c>
-      <c r="G28" s="31" t="s">
+      <c r="G28" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="H28" s="49"/>
+      <c r="H28" s="23"/>
     </row>
     <row r="29" spans="1:9" ht="12.75">
-      <c r="C29" s="61" t="s">
+      <c r="C29" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="D29" s="61" t="s">
+      <c r="D29" s="35" t="s">
         <v>132</v>
       </c>
-      <c r="E29" s="33">
+      <c r="E29" s="7">
         <v>5</v>
       </c>
-      <c r="F29" s="59" t="s">
+      <c r="F29" s="33" t="s">
         <v>133</v>
       </c>
-      <c r="G29" s="60" t="s">
+      <c r="G29" s="34" t="s">
         <v>134</v>
       </c>
-      <c r="H29" s="50" t="s">
+      <c r="H29" s="24" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="12.75">
-      <c r="C30" s="64"/>
-      <c r="D30" s="65" t="s">
+      <c r="C30" s="38"/>
+      <c r="D30" s="39" t="s">
         <v>136</v>
       </c>
-      <c r="E30" s="33">
+      <c r="E30" s="7">
         <v>6</v>
       </c>
-      <c r="F30" s="59" t="s">
+      <c r="F30" s="33" t="s">
         <v>137</v>
       </c>
-      <c r="G30" s="60" t="s">
+      <c r="G30" s="34" t="s">
         <v>138</v>
       </c>
-      <c r="H30" s="50" t="s">
+      <c r="H30" s="24" t="s">
         <v>139</v>
       </c>
     </row>
@@ -6765,761 +6636,761 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="118" t="s">
+      <c r="A1" s="112" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="120"/>
+      <c r="B1" s="113"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="114"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="118" t="s">
+      <c r="F1" s="112" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="120"/>
-      <c r="K1" s="97" t="s">
+      <c r="G1" s="113"/>
+      <c r="H1" s="113"/>
+      <c r="I1" s="114"/>
+      <c r="K1" s="71" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="121" t="s">
+      <c r="A2" s="115" t="s">
         <v>190</v>
       </c>
-      <c r="B2" s="88" t="s">
+      <c r="B2" s="62" t="s">
         <v>64</v>
       </c>
-      <c r="C2" s="53" t="s">
+      <c r="C2" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="32" t="s">
+      <c r="D2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="33">
+      <c r="E2" s="7">
         <v>1</v>
       </c>
-      <c r="F2" s="34" t="s">
+      <c r="F2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="35"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="122"/>
-      <c r="B3" s="88" t="s">
+      <c r="A3" s="116"/>
+      <c r="B3" s="62" t="s">
         <v>65</v>
       </c>
-      <c r="C3" s="53" t="s">
+      <c r="C3" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="32" t="s">
+      <c r="D3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="33">
+      <c r="E3" s="7">
         <v>2</v>
       </c>
-      <c r="F3" s="34" t="s">
+      <c r="F3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="35"/>
-      <c r="H3" s="43" t="s">
+      <c r="G3" s="9"/>
+      <c r="H3" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="I3" s="123" t="s">
+      <c r="I3" s="117" t="s">
         <v>192</v>
       </c>
-      <c r="K3" s="97" t="s">
+      <c r="K3" s="71" t="s">
         <v>207</v>
       </c>
-      <c r="L3" s="97"/>
+      <c r="L3" s="71"/>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="33">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="7">
         <v>3</v>
       </c>
-      <c r="F4" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="H4" s="43" t="s">
+      <c r="F4" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="I4" s="115"/>
-      <c r="K4" s="96" t="s">
+      <c r="I4" s="107"/>
+      <c r="K4" s="70" t="s">
         <v>80</v>
       </c>
-      <c r="L4" s="96" t="s">
+      <c r="L4" s="70" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" s="30"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="114" t="s">
+      <c r="A5" s="4"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="106" t="s">
         <v>59</v>
       </c>
-      <c r="D5" s="32" t="s">
+      <c r="D5" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="33">
+      <c r="E5" s="7">
         <v>4</v>
       </c>
-      <c r="F5" s="34" t="s">
+      <c r="F5" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="35"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
-      <c r="K5" s="96" t="s">
+      <c r="G5" s="9"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="K5" s="70" t="s">
         <v>204</v>
       </c>
-      <c r="L5" s="96" t="s">
+      <c r="L5" s="70" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" s="30"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="116"/>
-      <c r="D6" s="32" t="s">
+      <c r="A6" s="4"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="108"/>
+      <c r="D6" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="33">
+      <c r="E6" s="7">
         <v>5</v>
       </c>
-      <c r="F6" s="34" t="s">
+      <c r="F6" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="G6" s="34" t="s">
+      <c r="G6" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="89" t="s">
+      <c r="H6" s="63" t="s">
         <v>202</v>
       </c>
-      <c r="I6" s="89" t="s">
+      <c r="I6" s="63" t="s">
         <v>213</v>
       </c>
-      <c r="K6" s="96" t="s">
+      <c r="K6" s="70" t="s">
         <v>205</v>
       </c>
-      <c r="L6" s="96" t="s">
+      <c r="L6" s="70" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="7" spans="1:12">
-      <c r="A7" s="30"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="116"/>
-      <c r="D7" s="32" t="s">
+      <c r="A7" s="4"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="108"/>
+      <c r="D7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="33">
+      <c r="E7" s="7">
         <v>6</v>
       </c>
-      <c r="F7" s="38" t="s">
+      <c r="F7" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="G7" s="35"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="K7" s="96" t="s">
-        <v>12</v>
-      </c>
-      <c r="L7" s="96" t="s">
+      <c r="G7" s="9"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="K7" s="70" t="s">
+        <v>12</v>
+      </c>
+      <c r="L7" s="70" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:12">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="115"/>
-      <c r="D8" s="32" t="s">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="107"/>
+      <c r="D8" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E8" s="33">
+      <c r="E8" s="7">
         <v>7</v>
       </c>
-      <c r="F8" s="39" t="s">
+      <c r="F8" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="G8" s="38" t="s">
+      <c r="G8" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
     </row>
     <row r="9" spans="1:12">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" s="33">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="7">
         <v>8</v>
       </c>
-      <c r="F9" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="K9" s="97" t="s">
+      <c r="F9" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="K9" s="71" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="10" spans="1:12">
-      <c r="A10" s="92" t="s">
+      <c r="A10" s="66" t="s">
         <v>73</v>
       </c>
-      <c r="B10" s="93" t="s">
+      <c r="B10" s="67" t="s">
         <v>193</v>
       </c>
-      <c r="C10" s="114" t="s">
+      <c r="C10" s="106" t="s">
         <v>60</v>
       </c>
-      <c r="D10" s="32" t="s">
+      <c r="D10" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="E10" s="33">
+      <c r="E10" s="7">
         <v>9</v>
       </c>
-      <c r="F10" s="39" t="s">
+      <c r="F10" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="G10" s="38" t="s">
+      <c r="G10" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="K10" s="96" t="s">
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="K10" s="70" t="s">
         <v>202</v>
       </c>
-      <c r="L10" s="96" t="s">
+      <c r="L10" s="70" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="11" spans="1:12">
-      <c r="A11" s="94" t="s">
+      <c r="A11" s="68" t="s">
         <v>73</v>
       </c>
-      <c r="B11" s="95" t="s">
+      <c r="B11" s="69" t="s">
         <v>198</v>
       </c>
-      <c r="C11" s="133"/>
-      <c r="D11" s="32" t="s">
+      <c r="C11" s="111"/>
+      <c r="D11" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="E11" s="33">
+      <c r="E11" s="7">
         <v>10</v>
       </c>
-      <c r="F11" s="39" t="s">
+      <c r="F11" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="38" t="s">
+      <c r="G11" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="K11" s="96" t="s">
-        <v>12</v>
-      </c>
-      <c r="L11" s="96" t="s">
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="K11" s="70" t="s">
+        <v>12</v>
+      </c>
+      <c r="L11" s="70" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:12">
-      <c r="A12" s="54"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="116"/>
-      <c r="D12" s="32" t="s">
+      <c r="A12" s="28"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="108"/>
+      <c r="D12" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="E12" s="33">
+      <c r="E12" s="7">
         <v>11</v>
       </c>
-      <c r="F12" s="34" t="s">
+      <c r="F12" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="G12" s="35"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="K12" s="102" t="s">
+      <c r="G12" s="9"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="K12" s="76" t="s">
         <v>57</v>
       </c>
-      <c r="L12" s="102" t="s">
+      <c r="L12" s="76" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:12">
-      <c r="C13" s="115"/>
-      <c r="D13" s="32" t="s">
+      <c r="C13" s="107"/>
+      <c r="D13" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E13" s="33">
-        <v>12</v>
-      </c>
-      <c r="F13" s="39" t="s">
+      <c r="E13" s="7">
+        <v>12</v>
+      </c>
+      <c r="F13" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="G13" s="41"/>
-      <c r="H13" s="43" t="s">
+      <c r="G13" s="15"/>
+      <c r="H13" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="I13" s="43" t="s">
+      <c r="I13" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="K13" s="96" t="s">
+      <c r="K13" s="70" t="s">
         <v>54</v>
       </c>
-      <c r="L13" s="96" t="s">
+      <c r="L13" s="70" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:12">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" s="33">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" s="7">
         <v>13</v>
       </c>
-      <c r="F14" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="G14" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
-      <c r="K14" s="101"/>
-      <c r="L14" s="101"/>
+      <c r="F14" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="K14" s="75"/>
+      <c r="L14" s="75"/>
     </row>
     <row r="15" spans="1:12">
-      <c r="A15" s="114" t="s">
+      <c r="A15" s="106" t="s">
         <v>102</v>
       </c>
-      <c r="B15" s="43" t="s">
+      <c r="B15" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="C15" s="114" t="s">
+      <c r="C15" s="106" t="s">
         <v>61</v>
       </c>
-      <c r="D15" s="32" t="s">
+      <c r="D15" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="E15" s="33">
+      <c r="E15" s="7">
         <v>14</v>
       </c>
-      <c r="F15" s="39" t="s">
+      <c r="F15" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="G15" s="114" t="s">
+      <c r="G15" s="106" t="s">
         <v>62</v>
       </c>
-      <c r="H15" s="43" t="s">
+      <c r="H15" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="I15" s="114" t="s">
+      <c r="I15" s="106" t="s">
         <v>105</v>
       </c>
-      <c r="K15" s="103" t="s">
+      <c r="K15" s="77" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="16" spans="1:12">
-      <c r="A16" s="115"/>
-      <c r="B16" s="43" t="s">
+      <c r="A16" s="107"/>
+      <c r="B16" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="C16" s="116"/>
-      <c r="D16" s="39" t="s">
+      <c r="C16" s="108"/>
+      <c r="D16" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="E16" s="33">
+      <c r="E16" s="7">
         <v>15</v>
       </c>
-      <c r="F16" s="39" t="s">
+      <c r="F16" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="G16" s="115"/>
-      <c r="H16" s="43" t="s">
+      <c r="G16" s="107"/>
+      <c r="H16" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="I16" s="117"/>
-      <c r="K16" s="96" t="s">
+      <c r="I16" s="109"/>
+      <c r="K16" s="70" t="s">
         <v>5</v>
       </c>
-      <c r="L16" s="96" t="s">
+      <c r="L16" s="70" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="17" spans="1:12">
-      <c r="A17" s="114" t="s">
+      <c r="A17" s="106" t="s">
         <v>102</v>
       </c>
-      <c r="B17" s="43" t="s">
+      <c r="B17" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="C17" s="116"/>
-      <c r="D17" s="39" t="s">
+      <c r="C17" s="108"/>
+      <c r="D17" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="E17" s="33">
+      <c r="E17" s="7">
         <v>16</v>
       </c>
-      <c r="F17" s="39" t="s">
+      <c r="F17" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="G17" s="42" t="s">
+      <c r="G17" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="H17" s="8"/>
-      <c r="I17" s="54"/>
-      <c r="K17" s="96" t="s">
+      <c r="H17" s="2"/>
+      <c r="I17" s="28"/>
+      <c r="K17" s="70" t="s">
         <v>10</v>
       </c>
-      <c r="L17" s="96" t="s">
+      <c r="L17" s="70" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="18" spans="1:12">
-      <c r="A18" s="115"/>
-      <c r="B18" s="43" t="s">
+      <c r="A18" s="107"/>
+      <c r="B18" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="C18" s="115"/>
-      <c r="D18" s="32" t="s">
+      <c r="C18" s="107"/>
+      <c r="D18" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E18" s="33">
+      <c r="E18" s="7">
         <v>17</v>
       </c>
-      <c r="F18" s="39" t="s">
+      <c r="F18" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="G18" s="42" t="s">
+      <c r="G18" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="H18" s="8"/>
-      <c r="I18" s="54"/>
-      <c r="K18" s="96" t="s">
-        <v>12</v>
-      </c>
-      <c r="L18" s="96" t="s">
+      <c r="H18" s="2"/>
+      <c r="I18" s="28"/>
+      <c r="K18" s="70" t="s">
+        <v>12</v>
+      </c>
+      <c r="L18" s="70" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:12">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="D19" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="E19" s="33">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" s="7">
         <v>18</v>
       </c>
-      <c r="F19" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="G19" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8"/>
-      <c r="K19" s="96" t="s">
+      <c r="F19" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="K19" s="70" t="s">
         <v>202</v>
       </c>
-      <c r="L19" s="96" t="s">
+      <c r="L19" s="70" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="20" spans="1:12">
-      <c r="A20" s="135" t="s">
+      <c r="A20" s="127" t="s">
         <v>199</v>
       </c>
-      <c r="B20" s="95" t="s">
+      <c r="B20" s="69" t="s">
         <v>64</v>
       </c>
-      <c r="C20" s="53" t="s">
+      <c r="C20" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="D20" s="32" t="s">
+      <c r="D20" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="E20" s="33">
+      <c r="E20" s="7">
         <v>19</v>
       </c>
-      <c r="F20" s="39" t="s">
+      <c r="F20" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="G20" s="42" t="s">
+      <c r="G20" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="H20" s="43" t="s">
+      <c r="H20" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="I20" s="43" t="s">
+      <c r="I20" s="17" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="21" spans="1:12">
-      <c r="A21" s="136"/>
-      <c r="B21" s="95" t="s">
+      <c r="A21" s="128"/>
+      <c r="B21" s="69" t="s">
         <v>65</v>
       </c>
-      <c r="C21" s="53" t="s">
+      <c r="C21" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="D21" s="32" t="s">
+      <c r="D21" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E21" s="33">
+      <c r="E21" s="7">
         <v>20</v>
       </c>
-      <c r="F21" s="39" t="s">
+      <c r="F21" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="G21" s="42" t="s">
+      <c r="G21" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="H21" s="43" t="s">
+      <c r="H21" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="I21" s="43" t="s">
+      <c r="I21" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="K21" s="97" t="s">
+      <c r="K21" s="71" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="22" spans="1:12">
-      <c r="K22" s="96" t="s">
+      <c r="K22" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="L22" s="96" t="s">
+      <c r="L22" s="70" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="23" spans="1:12">
-      <c r="C23" s="44" t="s">
+      <c r="C23" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="K23" s="96" t="s">
+      <c r="K23" s="70" t="s">
         <v>47</v>
       </c>
-      <c r="L23" s="96" t="s">
+      <c r="L23" s="70" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="24" spans="1:12">
-      <c r="C24" s="55"/>
-      <c r="D24" s="37" t="s">
+      <c r="C24" s="29"/>
+      <c r="D24" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="E24" s="33"/>
-      <c r="F24" s="37" t="s">
+      <c r="E24" s="7"/>
+      <c r="F24" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="G24" s="56"/>
-      <c r="H24" s="100" t="s">
+      <c r="G24" s="30"/>
+      <c r="H24" s="74" t="s">
         <v>200</v>
       </c>
-      <c r="K24" s="96" t="s">
-        <v>12</v>
-      </c>
-      <c r="L24" s="96" t="s">
+      <c r="K24" s="70" t="s">
+        <v>12</v>
+      </c>
+      <c r="L24" s="70" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:12">
-      <c r="C25" s="57"/>
-      <c r="D25" s="58" t="s">
+      <c r="C25" s="31"/>
+      <c r="D25" s="32" t="s">
         <v>117</v>
       </c>
-      <c r="E25" s="33">
+      <c r="E25" s="7">
         <v>1</v>
       </c>
-      <c r="F25" s="59" t="s">
+      <c r="F25" s="33" t="s">
         <v>118</v>
       </c>
-      <c r="G25" s="59" t="s">
+      <c r="G25" s="33" t="s">
         <v>194</v>
       </c>
-      <c r="H25" s="87" t="s">
+      <c r="H25" s="61" t="s">
         <v>43</v>
       </c>
-      <c r="K25" s="96" t="s">
+      <c r="K25" s="70" t="s">
         <v>66</v>
       </c>
-      <c r="L25" s="96" t="s">
+      <c r="L25" s="70" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="26" spans="1:12">
-      <c r="C26" s="61" t="s">
+      <c r="C26" s="35" t="s">
         <v>121</v>
       </c>
-      <c r="D26" s="61" t="s">
+      <c r="D26" s="35" t="s">
         <v>122</v>
       </c>
-      <c r="E26" s="33">
+      <c r="E26" s="7">
         <v>2</v>
       </c>
-      <c r="F26" s="98" t="s">
+      <c r="F26" s="72" t="s">
         <v>123</v>
       </c>
-      <c r="G26" s="59" t="s">
+      <c r="G26" s="33" t="s">
         <v>195</v>
       </c>
-      <c r="H26" s="87" t="s">
+      <c r="H26" s="61" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="27" spans="1:12">
-      <c r="C27" s="61" t="s">
+      <c r="C27" s="35" t="s">
         <v>126</v>
       </c>
-      <c r="D27" s="61" t="s">
+      <c r="D27" s="35" t="s">
         <v>127</v>
       </c>
-      <c r="E27" s="33">
+      <c r="E27" s="7">
         <v>3</v>
       </c>
-      <c r="F27" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="G27" s="91"/>
-      <c r="H27" s="90"/>
-      <c r="K27" s="97" t="s">
+      <c r="F27" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G27" s="65"/>
+      <c r="H27" s="64"/>
+      <c r="K27" s="71" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="28" spans="1:12">
-      <c r="C28" s="61" t="s">
+      <c r="C28" s="35" t="s">
         <v>128</v>
       </c>
-      <c r="D28" s="61" t="s">
+      <c r="D28" s="35" t="s">
         <v>129</v>
       </c>
-      <c r="E28" s="33">
+      <c r="E28" s="7">
         <v>4</v>
       </c>
-      <c r="F28" s="63" t="s">
+      <c r="F28" s="37" t="s">
         <v>79</v>
       </c>
-      <c r="G28" s="31" t="s">
+      <c r="G28" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="H28" s="90"/>
-      <c r="K28" s="99" t="s">
+      <c r="H28" s="64"/>
+      <c r="K28" s="73" t="s">
         <v>206</v>
       </c>
-      <c r="L28" s="99" t="s">
+      <c r="L28" s="73" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="29" spans="1:12">
-      <c r="C29" s="61" t="s">
+      <c r="C29" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="D29" s="61" t="s">
+      <c r="D29" s="35" t="s">
         <v>132</v>
       </c>
-      <c r="E29" s="33">
+      <c r="E29" s="7">
         <v>5</v>
       </c>
-      <c r="F29" s="59" t="s">
+      <c r="F29" s="33" t="s">
         <v>133</v>
       </c>
-      <c r="G29" s="59" t="s">
+      <c r="G29" s="33" t="s">
         <v>196</v>
       </c>
-      <c r="H29" s="87" t="s">
+      <c r="H29" s="61" t="s">
         <v>48</v>
       </c>
-      <c r="K29" s="99" t="s">
+      <c r="K29" s="73" t="s">
         <v>66</v>
       </c>
-      <c r="L29" s="99" t="s">
+      <c r="L29" s="73" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="30" spans="1:12">
-      <c r="C30" s="64"/>
-      <c r="D30" s="65" t="s">
+      <c r="C30" s="38"/>
+      <c r="D30" s="39" t="s">
         <v>136</v>
       </c>
-      <c r="E30" s="33">
+      <c r="E30" s="7">
         <v>6</v>
       </c>
-      <c r="F30" s="59" t="s">
+      <c r="F30" s="33" t="s">
         <v>137</v>
       </c>
-      <c r="G30" s="59" t="s">
+      <c r="G30" s="33" t="s">
         <v>197</v>
       </c>
-      <c r="H30" s="87" t="s">
+      <c r="H30" s="61" t="s">
         <v>50</v>
       </c>
-      <c r="K30" s="99" t="s">
-        <v>12</v>
-      </c>
-      <c r="L30" s="99" t="s">
+      <c r="K30" s="73" t="s">
+        <v>12</v>
+      </c>
+      <c r="L30" s="73" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="32" spans="1:12">
-      <c r="A32" s="97" t="s">
+      <c r="A32" s="71" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="33" spans="1:5" s="97" customFormat="1">
-      <c r="A33" s="77" t="s">
+    <row r="33" spans="1:5" s="71" customFormat="1">
+      <c r="A33" s="51" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="34" spans="1:5">
-      <c r="A34" s="77" t="s">
+      <c r="A34" s="51" t="s">
         <v>218</v>
       </c>
-      <c r="E34" s="101"/>
+      <c r="E34" s="75"/>
     </row>
     <row r="35" spans="1:5">
-      <c r="E35" s="101"/>
+      <c r="E35" s="75"/>
     </row>
     <row r="36" spans="1:5">
-      <c r="E36" s="101"/>
+      <c r="E36" s="75"/>
     </row>
     <row r="37" spans="1:5">
-      <c r="A37" s="104"/>
-      <c r="E37" s="101"/>
+      <c r="A37" s="78"/>
+      <c r="E37" s="75"/>
     </row>
     <row r="38" spans="1:5">
-      <c r="C38" s="101"/>
-      <c r="E38" s="101"/>
+      <c r="C38" s="75"/>
+      <c r="E38" s="75"/>
     </row>
   </sheetData>
   <mergeCells count="12">

--- a/[00] Overview/[01] Pinout Scheme/Pinouts.xlsx
+++ b/[00] Overview/[01] Pinout Scheme/Pinouts.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samue\OneDrive\Documents\[01] Projects\[01] ScratchBuiltRobotics\[00] Overview\[01] Pinout Scheme\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamL3\Documents\GitHub\ScratchBuiltRobotics\[00] Overview\[01] Pinout Scheme\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4BE52A2-4262-4847-8318-30493A250C41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B01A3AB2-7D34-4C9D-AD7F-89CAFDF035E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Standard Pins" sheetId="13" r:id="rId1"/>
     <sheet name="All Pins" sheetId="1" r:id="rId2"/>
     <sheet name="Default Pins" sheetId="2" r:id="rId3"/>
-    <sheet name="BLEJoystickController Pins" sheetId="3" r:id="rId4"/>
+    <sheet name="Breadboard Joystick Controller" sheetId="3" r:id="rId4"/>
     <sheet name="AnalogToDigital" sheetId="4" r:id="rId5"/>
     <sheet name="BLESingleJoystick" sheetId="12" r:id="rId6"/>
     <sheet name=" Brain Pins" sheetId="5" r:id="rId7"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1075" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1078" uniqueCount="229">
   <si>
     <t>LEFT</t>
   </si>
@@ -707,6 +707,18 @@
   </si>
   <si>
     <t>Analog 2</t>
+  </si>
+  <si>
+    <t>Right Joystick</t>
+  </si>
+  <si>
+    <t>Left Joystick</t>
+  </si>
+  <si>
+    <t>L Joystick</t>
+  </si>
+  <si>
+    <t>R Joystick</t>
   </si>
 </sst>
 </file>
@@ -1355,7 +1367,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="142">
+  <cellXfs count="144">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1628,14 +1640,15 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1648,6 +1661,12 @@
     <xf numFmtId="0" fontId="14" fillId="14" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1658,16 +1677,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="14" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1687,8 +1696,17 @@
     <xf numFmtId="0" fontId="5" fillId="20" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1909,35 +1927,35 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:L30"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="12.42578125" customWidth="1"/>
-    <col min="3" max="3" width="11.85546875" customWidth="1"/>
-    <col min="4" max="4" width="11.42578125" customWidth="1"/>
-    <col min="5" max="5" width="3.7109375" customWidth="1"/>
-    <col min="6" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.7109375" customWidth="1"/>
-    <col min="9" max="9" width="14.140625" customWidth="1"/>
+    <col min="2" max="2" width="12.453125" customWidth="1"/>
+    <col min="3" max="3" width="11.81640625" customWidth="1"/>
+    <col min="4" max="4" width="11.453125" customWidth="1"/>
+    <col min="5" max="5" width="3.7265625" customWidth="1"/>
+    <col min="6" max="7" width="10.1796875" customWidth="1"/>
+    <col min="8" max="8" width="11.7265625" customWidth="1"/>
+    <col min="9" max="9" width="14.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A1" s="118" t="s">
+      <c r="A1" s="119" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="120"/>
+      <c r="B1" s="120"/>
+      <c r="C1" s="120"/>
+      <c r="D1" s="121"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="118" t="s">
+      <c r="F1" s="119" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="120"/>
+      <c r="G1" s="120"/>
+      <c r="H1" s="120"/>
+      <c r="I1" s="121"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A2" s="121" t="s">
+      <c r="A2" s="122" t="s">
         <v>190</v>
       </c>
       <c r="B2" s="88" t="s">
@@ -1960,7 +1978,7 @@
       <c r="I2" s="8"/>
     </row>
     <row r="3" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A3" s="122"/>
+      <c r="A3" s="123"/>
       <c r="B3" s="88" t="s">
         <v>65</v>
       </c>
@@ -1980,7 +1998,7 @@
       <c r="H3" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="I3" s="123" t="s">
+      <c r="I3" s="124" t="s">
         <v>192</v>
       </c>
       <c r="L3" s="36"/>
@@ -2006,12 +2024,12 @@
       <c r="H4" s="43" t="s">
         <v>68</v>
       </c>
-      <c r="I4" s="115"/>
+      <c r="I4" s="118"/>
     </row>
     <row r="5" spans="1:12" ht="15.75" customHeight="1">
       <c r="A5" s="30"/>
       <c r="B5" s="8"/>
-      <c r="C5" s="114" t="s">
+      <c r="C5" s="125" t="s">
         <v>59</v>
       </c>
       <c r="D5" s="32" t="s">
@@ -2030,7 +2048,7 @@
     <row r="6" spans="1:12" ht="15.75" customHeight="1">
       <c r="A6" s="30"/>
       <c r="B6" s="8"/>
-      <c r="C6" s="116"/>
+      <c r="C6" s="117"/>
       <c r="D6" s="32" t="s">
         <v>19</v>
       </c>
@@ -2053,7 +2071,7 @@
     <row r="7" spans="1:12" ht="15.75" customHeight="1">
       <c r="A7" s="30"/>
       <c r="B7" s="8"/>
-      <c r="C7" s="116"/>
+      <c r="C7" s="117"/>
       <c r="D7" s="32" t="s">
         <v>22</v>
       </c>
@@ -2070,7 +2088,7 @@
     <row r="8" spans="1:12" ht="15.75" customHeight="1">
       <c r="A8" s="8"/>
       <c r="B8" s="8"/>
-      <c r="C8" s="115"/>
+      <c r="C8" s="118"/>
       <c r="D8" s="32" t="s">
         <v>26</v>
       </c>
@@ -2113,10 +2131,10 @@
       <c r="A10" s="107" t="s">
         <v>73</v>
       </c>
-      <c r="B10" s="141" t="s">
+      <c r="B10" s="114" t="s">
         <v>193</v>
       </c>
-      <c r="C10" s="132" t="s">
+      <c r="C10" s="115" t="s">
         <v>60</v>
       </c>
       <c r="D10" s="32" t="s">
@@ -2143,7 +2161,7 @@
       <c r="B11" s="95" t="s">
         <v>221</v>
       </c>
-      <c r="C11" s="133"/>
+      <c r="C11" s="116"/>
       <c r="D11" s="32" t="s">
         <v>33</v>
       </c>
@@ -2164,7 +2182,7 @@
     <row r="12" spans="1:12" ht="15.75" customHeight="1">
       <c r="A12" s="54"/>
       <c r="B12" s="8"/>
-      <c r="C12" s="116"/>
+      <c r="C12" s="117"/>
       <c r="D12" s="32" t="s">
         <v>37</v>
       </c>
@@ -2179,7 +2197,7 @@
       <c r="I12" s="8"/>
     </row>
     <row r="13" spans="1:12" ht="15.75" customHeight="1">
-      <c r="C13" s="115"/>
+      <c r="C13" s="118"/>
       <c r="D13" s="32" t="s">
         <v>40</v>
       </c>
@@ -2219,13 +2237,13 @@
       <c r="I14" s="8"/>
     </row>
     <row r="15" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A15" s="114" t="s">
+      <c r="A15" s="125" t="s">
         <v>102</v>
       </c>
       <c r="B15" s="43" t="s">
         <v>103</v>
       </c>
-      <c r="C15" s="114" t="s">
+      <c r="C15" s="125" t="s">
         <v>61</v>
       </c>
       <c r="D15" s="32" t="s">
@@ -2237,22 +2255,22 @@
       <c r="F15" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="G15" s="114" t="s">
+      <c r="G15" s="125" t="s">
         <v>62</v>
       </c>
       <c r="H15" s="43" t="s">
         <v>104</v>
       </c>
-      <c r="I15" s="114" t="s">
+      <c r="I15" s="125" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A16" s="115"/>
+      <c r="A16" s="118"/>
       <c r="B16" s="43" t="s">
         <v>106</v>
       </c>
-      <c r="C16" s="116"/>
+      <c r="C16" s="117"/>
       <c r="D16" s="39" t="s">
         <v>46</v>
       </c>
@@ -2262,20 +2280,20 @@
       <c r="F16" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="G16" s="115"/>
+      <c r="G16" s="118"/>
       <c r="H16" s="43" t="s">
         <v>107</v>
       </c>
-      <c r="I16" s="117"/>
+      <c r="I16" s="126"/>
     </row>
     <row r="17" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A17" s="114" t="s">
+      <c r="A17" s="125" t="s">
         <v>102</v>
       </c>
       <c r="B17" s="43" t="s">
         <v>108</v>
       </c>
-      <c r="C17" s="116"/>
+      <c r="C17" s="117"/>
       <c r="D17" s="39" t="s">
         <v>48</v>
       </c>
@@ -2292,11 +2310,11 @@
       <c r="I17" s="54"/>
     </row>
     <row r="18" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A18" s="115"/>
+      <c r="A18" s="118"/>
       <c r="B18" s="43" t="s">
         <v>109</v>
       </c>
-      <c r="C18" s="115"/>
+      <c r="C18" s="118"/>
       <c r="D18" s="32" t="s">
         <v>50</v>
       </c>
@@ -2383,10 +2401,10 @@
         <v>112</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="12.75">
+    <row r="23" spans="1:9" ht="13">
       <c r="C23" s="44"/>
     </row>
-    <row r="24" spans="1:9" ht="12.75">
+    <row r="24" spans="1:9" ht="12.5">
       <c r="C24" s="111"/>
       <c r="D24" s="111"/>
       <c r="E24" s="8"/>
@@ -2394,7 +2412,7 @@
       <c r="G24" s="112"/>
       <c r="H24" s="113"/>
     </row>
-    <row r="25" spans="1:9" ht="12.75">
+    <row r="25" spans="1:9" ht="12.5">
       <c r="C25" s="111"/>
       <c r="D25" s="111"/>
       <c r="E25" s="8"/>
@@ -2402,7 +2420,7 @@
       <c r="G25" s="1"/>
       <c r="H25" s="113"/>
     </row>
-    <row r="26" spans="1:9" ht="12.75">
+    <row r="26" spans="1:9" ht="12.5">
       <c r="C26" s="29"/>
       <c r="D26" s="29"/>
       <c r="E26" s="8"/>
@@ -2410,7 +2428,7 @@
       <c r="G26" s="1"/>
       <c r="H26" s="113"/>
     </row>
-    <row r="27" spans="1:9" ht="12.75">
+    <row r="27" spans="1:9" ht="12.5">
       <c r="C27" s="29"/>
       <c r="D27" s="29"/>
       <c r="E27" s="8"/>
@@ -2418,7 +2436,7 @@
       <c r="G27" s="30"/>
       <c r="H27" s="113"/>
     </row>
-    <row r="28" spans="1:9" ht="12.75">
+    <row r="28" spans="1:9" ht="12.5">
       <c r="C28" s="29"/>
       <c r="D28" s="29"/>
       <c r="E28" s="8"/>
@@ -2426,7 +2444,7 @@
       <c r="G28" s="29"/>
       <c r="H28" s="113"/>
     </row>
-    <row r="29" spans="1:9" ht="12.75">
+    <row r="29" spans="1:9" ht="12.5">
       <c r="C29" s="29"/>
       <c r="D29" s="29"/>
       <c r="E29" s="8"/>
@@ -2434,7 +2452,7 @@
       <c r="G29" s="1"/>
       <c r="H29" s="113"/>
     </row>
-    <row r="30" spans="1:9" ht="12.75">
+    <row r="30" spans="1:9" ht="12.5">
       <c r="C30" s="29"/>
       <c r="D30" s="29"/>
       <c r="E30" s="8"/>
@@ -2444,17 +2462,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="C15:C18"/>
+    <mergeCell ref="G15:G16"/>
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="A17:A18"/>
     <mergeCell ref="C10:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="F1:I1"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="I3:I4"/>
     <mergeCell ref="C5:C8"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="C15:C18"/>
-    <mergeCell ref="G15:G16"/>
-    <mergeCell ref="I15:I16"/>
-    <mergeCell ref="A17:A18"/>
   </mergeCells>
   <printOptions horizontalCentered="1" gridLines="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -2465,41 +2483,41 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31540CD4-B126-4FE7-A4C7-88A45F1D742B}">
   <dimension ref="A1:L26"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultRowHeight="12.5"/>
   <cols>
-    <col min="1" max="1" width="10.5703125" customWidth="1"/>
-    <col min="2" max="2" width="10.28515625" customWidth="1"/>
-    <col min="3" max="3" width="16.28515625" customWidth="1"/>
+    <col min="1" max="1" width="10.54296875" customWidth="1"/>
+    <col min="2" max="2" width="10.26953125" customWidth="1"/>
+    <col min="3" max="3" width="16.26953125" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
-    <col min="6" max="6" width="11.140625" customWidth="1"/>
+    <col min="6" max="6" width="11.1796875" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="12.7109375" customWidth="1"/>
+    <col min="8" max="8" width="12.7265625" customWidth="1"/>
     <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="11.42578125" customWidth="1"/>
-    <col min="11" max="11" width="9.5703125" customWidth="1"/>
-    <col min="12" max="12" width="11.28515625" customWidth="1"/>
+    <col min="10" max="10" width="11.453125" customWidth="1"/>
+    <col min="11" max="11" width="9.54296875" customWidth="1"/>
+    <col min="12" max="12" width="11.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" s="118" t="s">
+    <row r="1" spans="1:12" ht="13">
+      <c r="A1" s="119" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="120"/>
+      <c r="B1" s="120"/>
+      <c r="C1" s="120"/>
+      <c r="D1" s="121"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="118" t="s">
+      <c r="F1" s="119" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="120"/>
+      <c r="G1" s="120"/>
+      <c r="H1" s="120"/>
+      <c r="I1" s="121"/>
       <c r="K1" s="97" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="121" t="s">
+      <c r="A2" s="122" t="s">
         <v>190</v>
       </c>
       <c r="B2" s="88" t="s">
@@ -2521,8 +2539,8 @@
       <c r="H2" s="8"/>
       <c r="I2" s="8"/>
     </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="122"/>
+    <row r="3" spans="1:12" ht="13">
+      <c r="A3" s="123"/>
       <c r="B3" s="88" t="s">
         <v>65</v>
       </c>
@@ -2542,7 +2560,7 @@
       <c r="H3" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="I3" s="123" t="s">
+      <c r="I3" s="124" t="s">
         <v>192</v>
       </c>
       <c r="K3" s="97" t="s">
@@ -2571,7 +2589,7 @@
       <c r="H4" s="43" t="s">
         <v>68</v>
       </c>
-      <c r="I4" s="115"/>
+      <c r="I4" s="118"/>
       <c r="K4" s="96" t="s">
         <v>66</v>
       </c>
@@ -2582,7 +2600,7 @@
     <row r="5" spans="1:12">
       <c r="A5" s="30"/>
       <c r="B5" s="8"/>
-      <c r="C5" s="114" t="s">
+      <c r="C5" s="125" t="s">
         <v>59</v>
       </c>
       <c r="D5" s="32" t="s">
@@ -2607,7 +2625,7 @@
     <row r="6" spans="1:12">
       <c r="A6" s="30"/>
       <c r="B6" s="8"/>
-      <c r="C6" s="116"/>
+      <c r="C6" s="117"/>
       <c r="D6" s="32" t="s">
         <v>19</v>
       </c>
@@ -2636,7 +2654,7 @@
     <row r="7" spans="1:12">
       <c r="A7" s="30"/>
       <c r="B7" s="8"/>
-      <c r="C7" s="116"/>
+      <c r="C7" s="117"/>
       <c r="D7" s="32" t="s">
         <v>22</v>
       </c>
@@ -2659,7 +2677,7 @@
     <row r="8" spans="1:12">
       <c r="A8" s="8"/>
       <c r="B8" s="8"/>
-      <c r="C8" s="115"/>
+      <c r="C8" s="118"/>
       <c r="D8" s="32" t="s">
         <v>26</v>
       </c>
@@ -2702,14 +2720,14 @@
       <c r="H9" s="8"/>
       <c r="I9" s="8"/>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:12" ht="13">
       <c r="A10" s="43" t="s">
         <v>73</v>
       </c>
       <c r="B10" s="89" t="s">
         <v>193</v>
       </c>
-      <c r="C10" s="114" t="s">
+      <c r="C10" s="125" t="s">
         <v>60</v>
       </c>
       <c r="D10" s="32" t="s">
@@ -2733,7 +2751,7 @@
     <row r="11" spans="1:12">
       <c r="A11" s="54"/>
       <c r="B11" s="8"/>
-      <c r="C11" s="116"/>
+      <c r="C11" s="117"/>
       <c r="D11" s="32" t="s">
         <v>33</v>
       </c>
@@ -2758,7 +2776,7 @@
     <row r="12" spans="1:12">
       <c r="A12" s="54"/>
       <c r="B12" s="8"/>
-      <c r="C12" s="116"/>
+      <c r="C12" s="117"/>
       <c r="D12" s="32" t="s">
         <v>37</v>
       </c>
@@ -2779,7 +2797,7 @@
       </c>
     </row>
     <row r="13" spans="1:12">
-      <c r="C13" s="115"/>
+      <c r="C13" s="118"/>
       <c r="D13" s="32" t="s">
         <v>40</v>
       </c>
@@ -2831,7 +2849,7 @@
       </c>
     </row>
     <row r="15" spans="1:12">
-      <c r="C15" s="137" t="s">
+      <c r="C15" s="136" t="s">
         <v>61</v>
       </c>
       <c r="D15" s="83" t="s">
@@ -2843,18 +2861,18 @@
       <c r="F15" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="G15" s="114" t="s">
+      <c r="G15" s="125" t="s">
         <v>62</v>
       </c>
       <c r="H15" s="43" t="s">
         <v>104</v>
       </c>
-      <c r="I15" s="134" t="s">
+      <c r="I15" s="133" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="16" spans="1:12">
-      <c r="C16" s="138"/>
+      <c r="C16" s="137"/>
       <c r="D16" s="84" t="s">
         <v>46</v>
       </c>
@@ -2864,14 +2882,14 @@
       <c r="F16" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="G16" s="115"/>
+      <c r="G16" s="118"/>
       <c r="H16" s="43" t="s">
         <v>107</v>
       </c>
-      <c r="I16" s="115"/>
+      <c r="I16" s="118"/>
     </row>
     <row r="17" spans="1:9">
-      <c r="C17" s="138"/>
+      <c r="C17" s="137"/>
       <c r="D17" s="84" t="s">
         <v>48</v>
       </c>
@@ -2888,7 +2906,7 @@
       <c r="I17" s="54"/>
     </row>
     <row r="18" spans="1:9">
-      <c r="C18" s="138"/>
+      <c r="C18" s="137"/>
       <c r="D18" s="83" t="s">
         <v>50</v>
       </c>
@@ -2926,7 +2944,7 @@
       <c r="I19" s="8"/>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="139" t="s">
+      <c r="A20" s="138" t="s">
         <v>189</v>
       </c>
       <c r="B20" s="88" t="s">
@@ -2955,7 +2973,7 @@
       </c>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="140"/>
+      <c r="A21" s="139"/>
       <c r="B21" s="88" t="s">
         <v>65</v>
       </c>
@@ -2981,7 +2999,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="23" spans="1:9">
+    <row r="23" spans="1:9" ht="13">
       <c r="C23" s="44"/>
     </row>
     <row r="26" spans="1:9">
@@ -3012,15 +3030,15 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:D16"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="4.42578125" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" customWidth="1"/>
-    <col min="3" max="3" width="19.5703125" customWidth="1"/>
+    <col min="1" max="1" width="4.453125" customWidth="1"/>
+    <col min="2" max="2" width="13.54296875" customWidth="1"/>
+    <col min="3" max="3" width="19.54296875" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="12.75">
+    <row r="1" spans="1:4" ht="13">
       <c r="A1" s="44" t="s">
         <v>140</v>
       </c>
@@ -3241,16 +3259,16 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{076B43BB-6571-4E49-8DE6-1A5CDADBA573}">
   <dimension ref="A1:E21"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultRowHeight="12.5"/>
   <cols>
-    <col min="1" max="1" width="5.140625" customWidth="1"/>
-    <col min="2" max="2" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.1796875" customWidth="1"/>
+    <col min="2" max="2" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.81640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.42578125" customWidth="1"/>
+    <col min="10" max="10" width="12.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" ht="13">
       <c r="A1" s="74" t="s">
         <v>180</v>
       </c>
@@ -3444,11 +3462,11 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:F16"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="14.42578125" customWidth="1"/>
-    <col min="3" max="3" width="4.28515625" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" customWidth="1"/>
+    <col min="1" max="1" width="14.453125" customWidth="1"/>
+    <col min="3" max="3" width="4.26953125" customWidth="1"/>
+    <col min="5" max="5" width="14.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" customHeight="1">
@@ -3659,27 +3677,27 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:I21"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="4" width="10.140625" customWidth="1"/>
-    <col min="5" max="5" width="3.7109375" customWidth="1"/>
-    <col min="6" max="9" width="10.140625" customWidth="1"/>
+    <col min="1" max="4" width="10.1796875" customWidth="1"/>
+    <col min="5" max="5" width="3.7265625" customWidth="1"/>
+    <col min="6" max="9" width="10.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A1" s="124" t="s">
+      <c r="A1" s="127" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="125"/>
-      <c r="C1" s="125"/>
-      <c r="D1" s="126"/>
+      <c r="B1" s="128"/>
+      <c r="C1" s="128"/>
+      <c r="D1" s="129"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="124" t="s">
+      <c r="F1" s="127" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="125"/>
-      <c r="H1" s="125"/>
-      <c r="I1" s="126"/>
+      <c r="G1" s="128"/>
+      <c r="H1" s="128"/>
+      <c r="I1" s="129"/>
     </row>
     <row r="2" spans="1:9" ht="15.75" customHeight="1">
       <c r="A2" s="2" t="s">
@@ -4156,27 +4174,27 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:L21"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="4" width="10.140625" customWidth="1"/>
-    <col min="5" max="5" width="3.7109375" customWidth="1"/>
-    <col min="6" max="9" width="10.140625" customWidth="1"/>
+    <col min="1" max="4" width="10.1796875" customWidth="1"/>
+    <col min="5" max="5" width="3.7265625" customWidth="1"/>
+    <col min="6" max="9" width="10.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A1" s="124" t="s">
+      <c r="A1" s="127" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="125"/>
-      <c r="C1" s="125"/>
-      <c r="D1" s="126"/>
+      <c r="B1" s="128"/>
+      <c r="C1" s="128"/>
+      <c r="D1" s="129"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="118" t="s">
+      <c r="F1" s="119" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="120"/>
+      <c r="G1" s="120"/>
+      <c r="H1" s="120"/>
+      <c r="I1" s="121"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" customHeight="1">
       <c r="A2" s="30"/>
@@ -4234,7 +4252,7 @@
     </row>
     <row r="5" spans="1:12" ht="15.75" customHeight="1">
       <c r="B5" s="30"/>
-      <c r="C5" s="114" t="s">
+      <c r="C5" s="125" t="s">
         <v>59</v>
       </c>
       <c r="D5" s="32" t="s">
@@ -4250,7 +4268,7 @@
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1">
       <c r="B6" s="30"/>
-      <c r="C6" s="116"/>
+      <c r="C6" s="117"/>
       <c r="D6" s="32" t="s">
         <v>19</v>
       </c>
@@ -4267,7 +4285,7 @@
     <row r="7" spans="1:12" ht="15.75" customHeight="1">
       <c r="A7" s="30"/>
       <c r="B7" s="30"/>
-      <c r="C7" s="116"/>
+      <c r="C7" s="117"/>
       <c r="D7" s="32" t="s">
         <v>22</v>
       </c>
@@ -4282,7 +4300,7 @@
     <row r="8" spans="1:12" ht="15.75" customHeight="1">
       <c r="A8" s="30"/>
       <c r="B8" s="30"/>
-      <c r="C8" s="115"/>
+      <c r="C8" s="118"/>
       <c r="D8" s="32" t="s">
         <v>26</v>
       </c>
@@ -4315,7 +4333,7 @@
     </row>
     <row r="10" spans="1:12" ht="15.75" customHeight="1">
       <c r="B10" s="30"/>
-      <c r="C10" s="114" t="s">
+      <c r="C10" s="125" t="s">
         <v>60</v>
       </c>
       <c r="D10" s="32" t="s">
@@ -4334,7 +4352,7 @@
     </row>
     <row r="11" spans="1:12" ht="15.75" customHeight="1">
       <c r="B11" s="30"/>
-      <c r="C11" s="116"/>
+      <c r="C11" s="117"/>
       <c r="D11" s="32" t="s">
         <v>33</v>
       </c>
@@ -4352,7 +4370,7 @@
     <row r="12" spans="1:12" ht="15.75" customHeight="1">
       <c r="A12" s="30"/>
       <c r="B12" s="30"/>
-      <c r="C12" s="116"/>
+      <c r="C12" s="117"/>
       <c r="D12" s="32" t="s">
         <v>37</v>
       </c>
@@ -4367,7 +4385,7 @@
     <row r="13" spans="1:12" ht="15.75" customHeight="1">
       <c r="A13" s="30"/>
       <c r="B13" s="30"/>
-      <c r="C13" s="115"/>
+      <c r="C13" s="118"/>
       <c r="D13" s="32" t="s">
         <v>40</v>
       </c>
@@ -4398,7 +4416,7 @@
     </row>
     <row r="15" spans="1:12" ht="15.75" customHeight="1">
       <c r="B15" s="30"/>
-      <c r="C15" s="114" t="s">
+      <c r="C15" s="125" t="s">
         <v>61</v>
       </c>
       <c r="D15" s="32" t="s">
@@ -4410,14 +4428,14 @@
       <c r="F15" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="G15" s="114" t="s">
+      <c r="G15" s="125" t="s">
         <v>62</v>
       </c>
       <c r="H15" s="30"/>
     </row>
     <row r="16" spans="1:12" ht="15.75" customHeight="1">
       <c r="B16" s="30"/>
-      <c r="C16" s="116"/>
+      <c r="C16" s="117"/>
       <c r="D16" s="39" t="s">
         <v>46</v>
       </c>
@@ -4427,13 +4445,13 @@
       <c r="F16" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="G16" s="115"/>
+      <c r="G16" s="118"/>
       <c r="H16" s="30"/>
     </row>
     <row r="17" spans="1:9" ht="15.75" customHeight="1">
       <c r="A17" s="30"/>
       <c r="B17" s="30"/>
-      <c r="C17" s="116"/>
+      <c r="C17" s="117"/>
       <c r="D17" s="39" t="s">
         <v>48</v>
       </c>
@@ -4451,7 +4469,7 @@
     <row r="18" spans="1:9" ht="15.75" customHeight="1">
       <c r="A18" s="30"/>
       <c r="B18" s="30"/>
-      <c r="C18" s="115"/>
+      <c r="C18" s="118"/>
       <c r="D18" s="32" t="s">
         <v>50</v>
       </c>
@@ -4544,30 +4562,30 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:L21"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="4" width="10.140625" customWidth="1"/>
-    <col min="5" max="5" width="3.7109375" customWidth="1"/>
-    <col min="6" max="9" width="10.140625" customWidth="1"/>
+    <col min="1" max="4" width="10.1796875" customWidth="1"/>
+    <col min="5" max="5" width="3.7265625" customWidth="1"/>
+    <col min="6" max="9" width="10.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A1" s="118" t="s">
+      <c r="A1" s="119" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="120"/>
+      <c r="B1" s="120"/>
+      <c r="C1" s="120"/>
+      <c r="D1" s="121"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="118" t="s">
+      <c r="F1" s="119" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="120"/>
+      <c r="G1" s="120"/>
+      <c r="H1" s="120"/>
+      <c r="I1" s="121"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A2" s="114" t="s">
+      <c r="A2" s="125" t="s">
         <v>63</v>
       </c>
       <c r="B2" s="43" t="s">
@@ -4590,7 +4608,7 @@
       <c r="I2" s="8"/>
     </row>
     <row r="3" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A3" s="115"/>
+      <c r="A3" s="118"/>
       <c r="B3" s="43" t="s">
         <v>65</v>
       </c>
@@ -4612,7 +4630,7 @@
       <c r="H3" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="I3" s="114" t="s">
+      <c r="I3" s="125" t="s">
         <v>67</v>
       </c>
       <c r="L3" s="36"/>
@@ -4638,7 +4656,7 @@
       <c r="H4" s="43" t="s">
         <v>68</v>
       </c>
-      <c r="I4" s="115"/>
+      <c r="I4" s="118"/>
     </row>
     <row r="5" spans="1:12" ht="15.75" customHeight="1">
       <c r="A5" s="43" t="s">
@@ -4647,7 +4665,7 @@
       <c r="B5" s="43" t="s">
         <v>70</v>
       </c>
-      <c r="C5" s="114" t="s">
+      <c r="C5" s="125" t="s">
         <v>59</v>
       </c>
       <c r="D5" s="32" t="s">
@@ -4670,7 +4688,7 @@
       <c r="B6" s="43" t="s">
         <v>70</v>
       </c>
-      <c r="C6" s="116"/>
+      <c r="C6" s="117"/>
       <c r="D6" s="32" t="s">
         <v>19</v>
       </c>
@@ -4684,19 +4702,16 @@
         <v>20</v>
       </c>
       <c r="H6" s="43" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I6" s="43" t="s">
-        <v>72</v>
-      </c>
-      <c r="J6" s="43" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15.75" customHeight="1">
       <c r="A7" s="8"/>
       <c r="B7" s="8"/>
-      <c r="C7" s="116"/>
+      <c r="C7" s="117"/>
       <c r="D7" s="32" t="s">
         <v>22</v>
       </c>
@@ -4713,7 +4728,7 @@
     <row r="8" spans="1:12" ht="15.75" customHeight="1">
       <c r="A8" s="8"/>
       <c r="B8" s="8"/>
-      <c r="C8" s="115"/>
+      <c r="C8" s="118"/>
       <c r="D8" s="32" t="s">
         <v>26</v>
       </c>
@@ -4757,7 +4772,7 @@
       <c r="B10" s="43" t="s">
         <v>71</v>
       </c>
-      <c r="C10" s="114" t="s">
+      <c r="C10" s="125" t="s">
         <v>60</v>
       </c>
       <c r="D10" s="32" t="s">
@@ -4778,7 +4793,7 @@
     <row r="11" spans="1:12" ht="15.75" customHeight="1">
       <c r="A11" s="8"/>
       <c r="B11" s="8"/>
-      <c r="C11" s="116"/>
+      <c r="C11" s="117"/>
       <c r="D11" s="32" t="s">
         <v>33</v>
       </c>
@@ -4797,7 +4812,7 @@
     <row r="12" spans="1:12" ht="15.75" customHeight="1">
       <c r="A12" s="8"/>
       <c r="B12" s="8"/>
-      <c r="C12" s="116"/>
+      <c r="C12" s="117"/>
       <c r="D12" s="32" t="s">
         <v>37</v>
       </c>
@@ -4814,7 +4829,7 @@
     <row r="13" spans="1:12" ht="15.75" customHeight="1">
       <c r="A13" s="8"/>
       <c r="B13" s="8"/>
-      <c r="C13" s="115"/>
+      <c r="C13" s="118"/>
       <c r="D13" s="32" t="s">
         <v>40</v>
       </c>
@@ -4854,7 +4869,7 @@
     <row r="15" spans="1:12" ht="15.75" customHeight="1">
       <c r="A15" s="30"/>
       <c r="B15" s="30"/>
-      <c r="C15" s="114" t="s">
+      <c r="C15" s="125" t="s">
         <v>61</v>
       </c>
       <c r="D15" s="32" t="s">
@@ -4866,7 +4881,7 @@
       <c r="F15" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="G15" s="114" t="s">
+      <c r="G15" s="125" t="s">
         <v>62</v>
       </c>
       <c r="H15" s="8"/>
@@ -4874,7 +4889,7 @@
     </row>
     <row r="16" spans="1:12" ht="15.75" customHeight="1">
       <c r="B16" s="30"/>
-      <c r="C16" s="116"/>
+      <c r="C16" s="117"/>
       <c r="D16" s="39" t="s">
         <v>46</v>
       </c>
@@ -4884,14 +4899,14 @@
       <c r="F16" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="G16" s="115"/>
+      <c r="G16" s="118"/>
       <c r="H16" s="8"/>
       <c r="I16" s="8"/>
     </row>
     <row r="17" spans="1:9" ht="15.75" customHeight="1">
       <c r="A17" s="8"/>
       <c r="B17" s="8"/>
-      <c r="C17" s="116"/>
+      <c r="C17" s="117"/>
       <c r="D17" s="39" t="s">
         <v>48</v>
       </c>
@@ -4910,7 +4925,7 @@
     <row r="18" spans="1:9" ht="15.75" customHeight="1">
       <c r="A18" s="8"/>
       <c r="B18" s="8"/>
-      <c r="C18" s="115"/>
+      <c r="C18" s="118"/>
       <c r="D18" s="32" t="s">
         <v>50</v>
       </c>
@@ -5012,12 +5027,12 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" customWidth="1"/>
+    <col min="1" max="1" width="4.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="12.75">
+    <row r="1" spans="1:4" ht="13">
       <c r="A1" s="33"/>
       <c r="B1" s="44" t="s">
         <v>77</v>
@@ -5151,27 +5166,28 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:L21"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="4" width="10.140625" customWidth="1"/>
-    <col min="5" max="5" width="3.7109375" customWidth="1"/>
-    <col min="6" max="9" width="10.140625" customWidth="1"/>
+    <col min="1" max="4" width="10.1796875" customWidth="1"/>
+    <col min="5" max="5" width="3.7265625" customWidth="1"/>
+    <col min="6" max="8" width="10.1796875" customWidth="1"/>
+    <col min="9" max="9" width="11.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A1" s="118" t="s">
+      <c r="A1" s="119" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="120"/>
+      <c r="B1" s="120"/>
+      <c r="C1" s="120"/>
+      <c r="D1" s="121"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="118" t="s">
+      <c r="F1" s="119" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="120"/>
+      <c r="G1" s="120"/>
+      <c r="H1" s="120"/>
+      <c r="I1" s="121"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" customHeight="1">
       <c r="A2" s="54"/>
@@ -5213,7 +5229,7 @@
       <c r="H3" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="I3" s="114" t="s">
+      <c r="I3" s="125" t="s">
         <v>67</v>
       </c>
       <c r="L3" s="36"/>
@@ -5236,19 +5252,19 @@
       <c r="G4" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="H4" s="43" t="s">
+      <c r="H4" s="89" t="s">
         <v>68</v>
       </c>
-      <c r="I4" s="115"/>
+      <c r="I4" s="118"/>
     </row>
     <row r="5" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A5" s="107" t="s">
-        <v>69</v>
+      <c r="A5" s="114" t="s">
+        <v>227</v>
       </c>
       <c r="B5" s="107" t="s">
         <v>70</v>
       </c>
-      <c r="C5" s="132" t="s">
+      <c r="C5" s="115" t="s">
         <v>59</v>
       </c>
       <c r="D5" s="32" t="s">
@@ -5265,9 +5281,13 @@
       <c r="I5" s="8"/>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="133"/>
+      <c r="A6" s="114" t="s">
+        <v>228</v>
+      </c>
+      <c r="B6" s="107" t="s">
+        <v>70</v>
+      </c>
+      <c r="C6" s="116"/>
       <c r="D6" s="32" t="s">
         <v>19</v>
       </c>
@@ -5291,7 +5311,7 @@
     <row r="7" spans="1:12" ht="15.75" customHeight="1">
       <c r="A7" s="8"/>
       <c r="B7" s="8"/>
-      <c r="C7" s="116"/>
+      <c r="C7" s="117"/>
       <c r="D7" s="32" t="s">
         <v>22</v>
       </c>
@@ -5308,7 +5328,7 @@
     <row r="8" spans="1:12" ht="15.75" customHeight="1">
       <c r="A8" s="8"/>
       <c r="B8" s="8"/>
-      <c r="C8" s="115"/>
+      <c r="C8" s="118"/>
       <c r="D8" s="32" t="s">
         <v>26</v>
       </c>
@@ -5318,11 +5338,15 @@
       <c r="F8" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="G8" s="38" t="s">
+      <c r="G8" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
+      <c r="H8" s="88" t="s">
+        <v>219</v>
+      </c>
+      <c r="I8" s="110" t="s">
+        <v>225</v>
+      </c>
     </row>
     <row r="9" spans="1:12" ht="15.75" customHeight="1">
       <c r="A9" s="8"/>
@@ -5339,11 +5363,11 @@
       <c r="F9" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
+      <c r="G9" s="52" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" s="141"/>
+      <c r="I9" s="143"/>
     </row>
     <row r="10" spans="1:12" ht="15.75" customHeight="1">
       <c r="A10" s="43" t="s">
@@ -5352,7 +5376,7 @@
       <c r="B10" s="43" t="s">
         <v>71</v>
       </c>
-      <c r="C10" s="114" t="s">
+      <c r="C10" s="125" t="s">
         <v>60</v>
       </c>
       <c r="D10" s="32" t="s">
@@ -5370,14 +5394,14 @@
       <c r="H10" s="95" t="s">
         <v>220</v>
       </c>
-      <c r="I10" s="130" t="s">
-        <v>69</v>
+      <c r="I10" s="122" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15.75" customHeight="1">
       <c r="A11" s="8"/>
       <c r="B11" s="8"/>
-      <c r="C11" s="116"/>
+      <c r="C11" s="117"/>
       <c r="D11" s="32" t="s">
         <v>33</v>
       </c>
@@ -5390,15 +5414,15 @@
       <c r="G11" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="H11" s="95" t="s">
+      <c r="H11" s="140" t="s">
         <v>219</v>
       </c>
-      <c r="I11" s="131"/>
+      <c r="I11" s="142"/>
     </row>
     <row r="12" spans="1:12" ht="15.75" customHeight="1">
       <c r="A12" s="8"/>
       <c r="B12" s="8"/>
-      <c r="C12" s="116"/>
+      <c r="C12" s="117"/>
       <c r="D12" s="32" t="s">
         <v>37</v>
       </c>
@@ -5415,7 +5439,7 @@
     <row r="13" spans="1:12" ht="15.75" customHeight="1">
       <c r="A13" s="8"/>
       <c r="B13" s="8"/>
-      <c r="C13" s="115"/>
+      <c r="C13" s="118"/>
       <c r="D13" s="32" t="s">
         <v>40</v>
       </c>
@@ -5455,7 +5479,7 @@
     <row r="15" spans="1:12" ht="15.75" customHeight="1">
       <c r="A15" s="54"/>
       <c r="B15" s="30"/>
-      <c r="C15" s="127" t="s">
+      <c r="C15" s="130" t="s">
         <v>61</v>
       </c>
       <c r="D15" s="32" t="s">
@@ -5467,7 +5491,7 @@
       <c r="F15" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="G15" s="114" t="s">
+      <c r="G15" s="125" t="s">
         <v>62</v>
       </c>
       <c r="H15" s="8"/>
@@ -5476,7 +5500,7 @@
     <row r="16" spans="1:12" ht="15.75" customHeight="1">
       <c r="A16" s="54"/>
       <c r="B16" s="30"/>
-      <c r="C16" s="128"/>
+      <c r="C16" s="131"/>
       <c r="D16" s="39" t="s">
         <v>46</v>
       </c>
@@ -5486,14 +5510,14 @@
       <c r="F16" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="G16" s="115"/>
+      <c r="G16" s="118"/>
       <c r="H16" s="8"/>
       <c r="I16" s="8"/>
     </row>
     <row r="17" spans="1:9" ht="15.75" customHeight="1">
       <c r="A17" s="8"/>
       <c r="B17" s="8"/>
-      <c r="C17" s="128"/>
+      <c r="C17" s="131"/>
       <c r="D17" s="39" t="s">
         <v>48</v>
       </c>
@@ -5512,7 +5536,7 @@
     <row r="18" spans="1:9" ht="15.75" customHeight="1">
       <c r="A18" s="8"/>
       <c r="B18" s="8"/>
-      <c r="C18" s="129"/>
+      <c r="C18" s="132"/>
       <c r="D18" s="32" t="s">
         <v>50</v>
       </c>
@@ -5614,30 +5638,30 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:L21"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="4" width="10.140625" customWidth="1"/>
-    <col min="5" max="5" width="3.7109375" customWidth="1"/>
-    <col min="6" max="9" width="10.140625" customWidth="1"/>
+    <col min="1" max="4" width="10.1796875" customWidth="1"/>
+    <col min="5" max="5" width="3.7265625" customWidth="1"/>
+    <col min="6" max="9" width="10.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A1" s="118" t="s">
+      <c r="A1" s="119" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="120"/>
+      <c r="B1" s="120"/>
+      <c r="C1" s="120"/>
+      <c r="D1" s="121"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="118" t="s">
+      <c r="F1" s="119" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="120"/>
+      <c r="G1" s="120"/>
+      <c r="H1" s="120"/>
+      <c r="I1" s="121"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A2" s="114" t="s">
+      <c r="A2" s="125" t="s">
         <v>94</v>
       </c>
       <c r="B2" s="43" t="s">
@@ -5660,7 +5684,7 @@
       <c r="I2" s="8"/>
     </row>
     <row r="3" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A3" s="115"/>
+      <c r="A3" s="118"/>
       <c r="B3" s="43" t="s">
         <v>64</v>
       </c>
@@ -5680,7 +5704,7 @@
       <c r="H3" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="I3" s="114" t="s">
+      <c r="I3" s="125" t="s">
         <v>67</v>
       </c>
       <c r="L3" s="36"/>
@@ -5706,16 +5730,16 @@
       <c r="H4" s="43" t="s">
         <v>68</v>
       </c>
-      <c r="I4" s="115"/>
+      <c r="I4" s="118"/>
     </row>
     <row r="5" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A5" s="114" t="s">
+      <c r="A5" s="125" t="s">
         <v>95</v>
       </c>
       <c r="B5" s="43" t="s">
         <v>70</v>
       </c>
-      <c r="C5" s="114" t="s">
+      <c r="C5" s="125" t="s">
         <v>59</v>
       </c>
       <c r="D5" s="32" t="s">
@@ -5732,11 +5756,11 @@
       <c r="I5" s="8"/>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A6" s="116"/>
+      <c r="A6" s="117"/>
       <c r="B6" s="43" t="s">
         <v>96</v>
       </c>
-      <c r="C6" s="116"/>
+      <c r="C6" s="117"/>
       <c r="D6" s="32" t="s">
         <v>19</v>
       </c>
@@ -5760,11 +5784,11 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A7" s="115"/>
+      <c r="A7" s="118"/>
       <c r="B7" s="43" t="s">
         <v>97</v>
       </c>
-      <c r="C7" s="116"/>
+      <c r="C7" s="117"/>
       <c r="D7" s="32" t="s">
         <v>22</v>
       </c>
@@ -5781,7 +5805,7 @@
     <row r="8" spans="1:12" ht="15.75" customHeight="1">
       <c r="A8" s="8"/>
       <c r="B8" s="8"/>
-      <c r="C8" s="115"/>
+      <c r="C8" s="118"/>
       <c r="D8" s="32" t="s">
         <v>26</v>
       </c>
@@ -5819,13 +5843,13 @@
       <c r="I9" s="8"/>
     </row>
     <row r="10" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A10" s="114" t="s">
+      <c r="A10" s="125" t="s">
         <v>98</v>
       </c>
       <c r="B10" s="43" t="s">
         <v>99</v>
       </c>
-      <c r="C10" s="114" t="s">
+      <c r="C10" s="125" t="s">
         <v>60</v>
       </c>
       <c r="D10" s="32" t="s">
@@ -5844,11 +5868,11 @@
       <c r="I10" s="8"/>
     </row>
     <row r="11" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A11" s="116"/>
+      <c r="A11" s="117"/>
       <c r="B11" s="43" t="s">
         <v>100</v>
       </c>
-      <c r="C11" s="116"/>
+      <c r="C11" s="117"/>
       <c r="D11" s="32" t="s">
         <v>33</v>
       </c>
@@ -5865,11 +5889,11 @@
       <c r="I11" s="8"/>
     </row>
     <row r="12" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A12" s="115"/>
+      <c r="A12" s="118"/>
       <c r="B12" s="43" t="s">
         <v>101</v>
       </c>
-      <c r="C12" s="116"/>
+      <c r="C12" s="117"/>
       <c r="D12" s="32" t="s">
         <v>37</v>
       </c>
@@ -5890,7 +5914,7 @@
       <c r="B13" s="43" t="s">
         <v>71</v>
       </c>
-      <c r="C13" s="115"/>
+      <c r="C13" s="118"/>
       <c r="D13" s="32" t="s">
         <v>40</v>
       </c>
@@ -5930,13 +5954,13 @@
       <c r="I14" s="8"/>
     </row>
     <row r="15" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A15" s="114" t="s">
+      <c r="A15" s="125" t="s">
         <v>102</v>
       </c>
       <c r="B15" s="43" t="s">
         <v>103</v>
       </c>
-      <c r="C15" s="114" t="s">
+      <c r="C15" s="125" t="s">
         <v>61</v>
       </c>
       <c r="D15" s="32" t="s">
@@ -5948,22 +5972,22 @@
       <c r="F15" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="G15" s="114" t="s">
+      <c r="G15" s="125" t="s">
         <v>62</v>
       </c>
       <c r="H15" s="43" t="s">
         <v>104</v>
       </c>
-      <c r="I15" s="134" t="s">
+      <c r="I15" s="133" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A16" s="115"/>
+      <c r="A16" s="118"/>
       <c r="B16" s="43" t="s">
         <v>106</v>
       </c>
-      <c r="C16" s="116"/>
+      <c r="C16" s="117"/>
       <c r="D16" s="39" t="s">
         <v>46</v>
       </c>
@@ -5973,20 +5997,20 @@
       <c r="F16" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="G16" s="115"/>
+      <c r="G16" s="118"/>
       <c r="H16" s="43" t="s">
         <v>107</v>
       </c>
-      <c r="I16" s="115"/>
+      <c r="I16" s="118"/>
     </row>
     <row r="17" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A17" s="114" t="s">
+      <c r="A17" s="125" t="s">
         <v>102</v>
       </c>
       <c r="B17" s="43" t="s">
         <v>108</v>
       </c>
-      <c r="C17" s="116"/>
+      <c r="C17" s="117"/>
       <c r="D17" s="39" t="s">
         <v>48</v>
       </c>
@@ -6002,16 +6026,16 @@
       <c r="H17" s="43" t="s">
         <v>64</v>
       </c>
-      <c r="I17" s="114" t="s">
+      <c r="I17" s="125" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A18" s="115"/>
+      <c r="A18" s="118"/>
       <c r="B18" s="43" t="s">
         <v>109</v>
       </c>
-      <c r="C18" s="115"/>
+      <c r="C18" s="118"/>
       <c r="D18" s="32" t="s">
         <v>50</v>
       </c>
@@ -6027,7 +6051,7 @@
       <c r="H18" s="43" t="s">
         <v>110</v>
       </c>
-      <c r="I18" s="115"/>
+      <c r="I18" s="118"/>
     </row>
     <row r="19" spans="1:9" ht="15.75" customHeight="1">
       <c r="A19" s="8"/>
@@ -6129,35 +6153,35 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:L30"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="14.140625" customWidth="1"/>
-    <col min="2" max="2" width="13.85546875" customWidth="1"/>
-    <col min="3" max="3" width="11.85546875" customWidth="1"/>
-    <col min="4" max="4" width="11.42578125" customWidth="1"/>
-    <col min="5" max="5" width="3.7109375" customWidth="1"/>
-    <col min="6" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.7109375" customWidth="1"/>
-    <col min="9" max="9" width="14.140625" customWidth="1"/>
+    <col min="1" max="1" width="14.1796875" customWidth="1"/>
+    <col min="2" max="2" width="13.81640625" customWidth="1"/>
+    <col min="3" max="3" width="11.81640625" customWidth="1"/>
+    <col min="4" max="4" width="11.453125" customWidth="1"/>
+    <col min="5" max="5" width="3.7265625" customWidth="1"/>
+    <col min="6" max="7" width="10.1796875" customWidth="1"/>
+    <col min="8" max="8" width="11.7265625" customWidth="1"/>
+    <col min="9" max="9" width="14.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A1" s="118" t="s">
+      <c r="A1" s="119" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="120"/>
+      <c r="B1" s="120"/>
+      <c r="C1" s="120"/>
+      <c r="D1" s="121"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="118" t="s">
+      <c r="F1" s="119" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="120"/>
+      <c r="G1" s="120"/>
+      <c r="H1" s="120"/>
+      <c r="I1" s="121"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A2" s="121" t="s">
+      <c r="A2" s="122" t="s">
         <v>190</v>
       </c>
       <c r="B2" s="88" t="s">
@@ -6180,7 +6204,7 @@
       <c r="I2" s="8"/>
     </row>
     <row r="3" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A3" s="122"/>
+      <c r="A3" s="123"/>
       <c r="B3" s="88" t="s">
         <v>65</v>
       </c>
@@ -6200,7 +6224,7 @@
       <c r="H3" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="I3" s="123" t="s">
+      <c r="I3" s="124" t="s">
         <v>192</v>
       </c>
       <c r="L3" s="36"/>
@@ -6226,12 +6250,12 @@
       <c r="H4" s="43" t="s">
         <v>68</v>
       </c>
-      <c r="I4" s="115"/>
+      <c r="I4" s="118"/>
     </row>
     <row r="5" spans="1:12" ht="15.75" customHeight="1">
       <c r="A5" s="30"/>
       <c r="B5" s="8"/>
-      <c r="C5" s="114" t="s">
+      <c r="C5" s="125" t="s">
         <v>59</v>
       </c>
       <c r="D5" s="32" t="s">
@@ -6250,7 +6274,7 @@
     <row r="6" spans="1:12" ht="15.75" customHeight="1">
       <c r="A6" s="30"/>
       <c r="B6" s="8"/>
-      <c r="C6" s="116"/>
+      <c r="C6" s="117"/>
       <c r="D6" s="32" t="s">
         <v>19</v>
       </c>
@@ -6276,7 +6300,7 @@
     <row r="7" spans="1:12" ht="15.75" customHeight="1">
       <c r="A7" s="30"/>
       <c r="B7" s="8"/>
-      <c r="C7" s="116"/>
+      <c r="C7" s="117"/>
       <c r="D7" s="32" t="s">
         <v>22</v>
       </c>
@@ -6293,7 +6317,7 @@
     <row r="8" spans="1:12" ht="15.75" customHeight="1">
       <c r="A8" s="8"/>
       <c r="B8" s="8"/>
-      <c r="C8" s="115"/>
+      <c r="C8" s="118"/>
       <c r="D8" s="32" t="s">
         <v>26</v>
       </c>
@@ -6337,7 +6361,7 @@
       <c r="B10" s="89" t="s">
         <v>193</v>
       </c>
-      <c r="C10" s="114" t="s">
+      <c r="C10" s="125" t="s">
         <v>60</v>
       </c>
       <c r="D10" s="32" t="s">
@@ -6358,7 +6382,7 @@
     <row r="11" spans="1:12" ht="15.75" customHeight="1">
       <c r="A11" s="54"/>
       <c r="B11" s="8"/>
-      <c r="C11" s="116"/>
+      <c r="C11" s="117"/>
       <c r="D11" s="32" t="s">
         <v>33</v>
       </c>
@@ -6377,7 +6401,7 @@
     <row r="12" spans="1:12" ht="15.75" customHeight="1">
       <c r="A12" s="54"/>
       <c r="B12" s="8"/>
-      <c r="C12" s="116"/>
+      <c r="C12" s="117"/>
       <c r="D12" s="32" t="s">
         <v>37</v>
       </c>
@@ -6392,7 +6416,7 @@
       <c r="I12" s="8"/>
     </row>
     <row r="13" spans="1:12" ht="15.75" customHeight="1">
-      <c r="C13" s="115"/>
+      <c r="C13" s="118"/>
       <c r="D13" s="32" t="s">
         <v>40</v>
       </c>
@@ -6432,13 +6456,13 @@
       <c r="I14" s="8"/>
     </row>
     <row r="15" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A15" s="114" t="s">
+      <c r="A15" s="125" t="s">
         <v>102</v>
       </c>
       <c r="B15" s="43" t="s">
         <v>103</v>
       </c>
-      <c r="C15" s="114" t="s">
+      <c r="C15" s="125" t="s">
         <v>61</v>
       </c>
       <c r="D15" s="32" t="s">
@@ -6450,22 +6474,22 @@
       <c r="F15" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="G15" s="114" t="s">
+      <c r="G15" s="125" t="s">
         <v>62</v>
       </c>
       <c r="H15" s="43" t="s">
         <v>104</v>
       </c>
-      <c r="I15" s="114" t="s">
+      <c r="I15" s="125" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A16" s="115"/>
+      <c r="A16" s="118"/>
       <c r="B16" s="43" t="s">
         <v>106</v>
       </c>
-      <c r="C16" s="116"/>
+      <c r="C16" s="117"/>
       <c r="D16" s="39" t="s">
         <v>46</v>
       </c>
@@ -6475,20 +6499,20 @@
       <c r="F16" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="G16" s="115"/>
+      <c r="G16" s="118"/>
       <c r="H16" s="43" t="s">
         <v>107</v>
       </c>
-      <c r="I16" s="117"/>
+      <c r="I16" s="126"/>
     </row>
     <row r="17" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A17" s="114" t="s">
+      <c r="A17" s="125" t="s">
         <v>102</v>
       </c>
       <c r="B17" s="43" t="s">
         <v>108</v>
       </c>
-      <c r="C17" s="116"/>
+      <c r="C17" s="117"/>
       <c r="D17" s="39" t="s">
         <v>48</v>
       </c>
@@ -6505,11 +6529,11 @@
       <c r="I17" s="54"/>
     </row>
     <row r="18" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A18" s="115"/>
+      <c r="A18" s="118"/>
       <c r="B18" s="43" t="s">
         <v>109</v>
       </c>
-      <c r="C18" s="115"/>
+      <c r="C18" s="118"/>
       <c r="D18" s="32" t="s">
         <v>50</v>
       </c>
@@ -6596,12 +6620,12 @@
         <v>112</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="12.75">
+    <row r="23" spans="1:9" ht="13">
       <c r="C23" s="44" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="12.75">
+    <row r="24" spans="1:9" ht="12.5">
       <c r="C24" s="55"/>
       <c r="D24" s="37" t="s">
         <v>114</v>
@@ -6615,7 +6639,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="12.75">
+    <row r="25" spans="1:9" ht="12.5">
       <c r="C25" s="57"/>
       <c r="D25" s="58" t="s">
         <v>117</v>
@@ -6633,7 +6657,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="12.75">
+    <row r="26" spans="1:9" ht="12.5">
       <c r="C26" s="61" t="s">
         <v>121</v>
       </c>
@@ -6653,7 +6677,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="12.75">
+    <row r="27" spans="1:9" ht="12.5">
       <c r="C27" s="61" t="s">
         <v>126</v>
       </c>
@@ -6669,7 +6693,7 @@
       <c r="G27" s="62"/>
       <c r="H27" s="49"/>
     </row>
-    <row r="28" spans="1:9" ht="12.75">
+    <row r="28" spans="1:9" ht="12.5">
       <c r="C28" s="61" t="s">
         <v>128</v>
       </c>
@@ -6687,7 +6711,7 @@
       </c>
       <c r="H28" s="49"/>
     </row>
-    <row r="29" spans="1:9" ht="12.75">
+    <row r="29" spans="1:9" ht="12.5">
       <c r="C29" s="61" t="s">
         <v>131</v>
       </c>
@@ -6707,7 +6731,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="12.75">
+    <row r="30" spans="1:9" ht="12.5">
       <c r="C30" s="64"/>
       <c r="D30" s="65" t="s">
         <v>136</v>
@@ -6751,39 +6775,39 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L38"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultRowHeight="12.5"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.54296875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="6" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" customWidth="1"/>
+    <col min="6" max="6" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.7265625" customWidth="1"/>
     <col min="8" max="8" width="13" customWidth="1"/>
-    <col min="9" max="9" width="13.85546875" customWidth="1"/>
-    <col min="11" max="11" width="12.42578125" customWidth="1"/>
-    <col min="12" max="12" width="11.5703125" customWidth="1"/>
+    <col min="9" max="9" width="13.81640625" customWidth="1"/>
+    <col min="11" max="11" width="12.453125" customWidth="1"/>
+    <col min="12" max="12" width="11.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" s="118" t="s">
+    <row r="1" spans="1:12" ht="13">
+      <c r="A1" s="119" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="120"/>
+      <c r="B1" s="120"/>
+      <c r="C1" s="120"/>
+      <c r="D1" s="121"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="118" t="s">
+      <c r="F1" s="119" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="120"/>
+      <c r="G1" s="120"/>
+      <c r="H1" s="120"/>
+      <c r="I1" s="121"/>
       <c r="K1" s="97" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="121" t="s">
+      <c r="A2" s="122" t="s">
         <v>190</v>
       </c>
       <c r="B2" s="88" t="s">
@@ -6805,8 +6829,8 @@
       <c r="H2" s="8"/>
       <c r="I2" s="8"/>
     </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="122"/>
+    <row r="3" spans="1:12" ht="13">
+      <c r="A3" s="123"/>
       <c r="B3" s="88" t="s">
         <v>65</v>
       </c>
@@ -6826,7 +6850,7 @@
       <c r="H3" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="I3" s="123" t="s">
+      <c r="I3" s="124" t="s">
         <v>192</v>
       </c>
       <c r="K3" s="97" t="s">
@@ -6855,7 +6879,7 @@
       <c r="H4" s="43" t="s">
         <v>68</v>
       </c>
-      <c r="I4" s="115"/>
+      <c r="I4" s="118"/>
       <c r="K4" s="96" t="s">
         <v>80</v>
       </c>
@@ -6866,7 +6890,7 @@
     <row r="5" spans="1:12">
       <c r="A5" s="30"/>
       <c r="B5" s="8"/>
-      <c r="C5" s="114" t="s">
+      <c r="C5" s="125" t="s">
         <v>59</v>
       </c>
       <c r="D5" s="32" t="s">
@@ -6891,7 +6915,7 @@
     <row r="6" spans="1:12">
       <c r="A6" s="30"/>
       <c r="B6" s="8"/>
-      <c r="C6" s="116"/>
+      <c r="C6" s="117"/>
       <c r="D6" s="32" t="s">
         <v>19</v>
       </c>
@@ -6920,7 +6944,7 @@
     <row r="7" spans="1:12">
       <c r="A7" s="30"/>
       <c r="B7" s="8"/>
-      <c r="C7" s="116"/>
+      <c r="C7" s="117"/>
       <c r="D7" s="32" t="s">
         <v>22</v>
       </c>
@@ -6943,7 +6967,7 @@
     <row r="8" spans="1:12">
       <c r="A8" s="8"/>
       <c r="B8" s="8"/>
-      <c r="C8" s="115"/>
+      <c r="C8" s="118"/>
       <c r="D8" s="32" t="s">
         <v>26</v>
       </c>
@@ -6959,7 +6983,7 @@
       <c r="H8" s="8"/>
       <c r="I8" s="8"/>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:12" ht="13">
       <c r="A9" s="8"/>
       <c r="B9" s="8"/>
       <c r="C9" s="37" t="s">
@@ -6990,7 +7014,7 @@
       <c r="B10" s="93" t="s">
         <v>193</v>
       </c>
-      <c r="C10" s="114" t="s">
+      <c r="C10" s="125" t="s">
         <v>60</v>
       </c>
       <c r="D10" s="32" t="s">
@@ -7021,7 +7045,7 @@
       <c r="B11" s="95" t="s">
         <v>198</v>
       </c>
-      <c r="C11" s="133"/>
+      <c r="C11" s="116"/>
       <c r="D11" s="32" t="s">
         <v>33</v>
       </c>
@@ -7046,7 +7070,7 @@
     <row r="12" spans="1:12">
       <c r="A12" s="54"/>
       <c r="B12" s="8"/>
-      <c r="C12" s="116"/>
+      <c r="C12" s="117"/>
       <c r="D12" s="32" t="s">
         <v>37</v>
       </c>
@@ -7067,7 +7091,7 @@
       </c>
     </row>
     <row r="13" spans="1:12">
-      <c r="C13" s="115"/>
+      <c r="C13" s="118"/>
       <c r="D13" s="32" t="s">
         <v>40</v>
       </c>
@@ -7114,14 +7138,14 @@
       <c r="K14" s="101"/>
       <c r="L14" s="101"/>
     </row>
-    <row r="15" spans="1:12">
-      <c r="A15" s="114" t="s">
+    <row r="15" spans="1:12" ht="13">
+      <c r="A15" s="125" t="s">
         <v>102</v>
       </c>
       <c r="B15" s="43" t="s">
         <v>103</v>
       </c>
-      <c r="C15" s="114" t="s">
+      <c r="C15" s="125" t="s">
         <v>61</v>
       </c>
       <c r="D15" s="32" t="s">
@@ -7133,13 +7157,13 @@
       <c r="F15" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="G15" s="114" t="s">
+      <c r="G15" s="125" t="s">
         <v>62</v>
       </c>
       <c r="H15" s="43" t="s">
         <v>104</v>
       </c>
-      <c r="I15" s="114" t="s">
+      <c r="I15" s="125" t="s">
         <v>105</v>
       </c>
       <c r="K15" s="103" t="s">
@@ -7147,11 +7171,11 @@
       </c>
     </row>
     <row r="16" spans="1:12">
-      <c r="A16" s="115"/>
+      <c r="A16" s="118"/>
       <c r="B16" s="43" t="s">
         <v>106</v>
       </c>
-      <c r="C16" s="116"/>
+      <c r="C16" s="117"/>
       <c r="D16" s="39" t="s">
         <v>46</v>
       </c>
@@ -7161,11 +7185,11 @@
       <c r="F16" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="G16" s="115"/>
+      <c r="G16" s="118"/>
       <c r="H16" s="43" t="s">
         <v>107</v>
       </c>
-      <c r="I16" s="117"/>
+      <c r="I16" s="126"/>
       <c r="K16" s="96" t="s">
         <v>5</v>
       </c>
@@ -7174,13 +7198,13 @@
       </c>
     </row>
     <row r="17" spans="1:12">
-      <c r="A17" s="114" t="s">
+      <c r="A17" s="125" t="s">
         <v>102</v>
       </c>
       <c r="B17" s="43" t="s">
         <v>108</v>
       </c>
-      <c r="C17" s="116"/>
+      <c r="C17" s="117"/>
       <c r="D17" s="39" t="s">
         <v>48</v>
       </c>
@@ -7203,11 +7227,11 @@
       </c>
     </row>
     <row r="18" spans="1:12">
-      <c r="A18" s="115"/>
+      <c r="A18" s="118"/>
       <c r="B18" s="43" t="s">
         <v>109</v>
       </c>
-      <c r="C18" s="115"/>
+      <c r="C18" s="118"/>
       <c r="D18" s="32" t="s">
         <v>50</v>
       </c>
@@ -7257,7 +7281,7 @@
       </c>
     </row>
     <row r="20" spans="1:12">
-      <c r="A20" s="135" t="s">
+      <c r="A20" s="134" t="s">
         <v>199</v>
       </c>
       <c r="B20" s="95" t="s">
@@ -7285,8 +7309,8 @@
         <v>112</v>
       </c>
     </row>
-    <row r="21" spans="1:12">
-      <c r="A21" s="136"/>
+    <row r="21" spans="1:12" ht="13">
+      <c r="A21" s="135"/>
       <c r="B21" s="95" t="s">
         <v>65</v>
       </c>
@@ -7323,7 +7347,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="23" spans="1:12">
+    <row r="23" spans="1:12" ht="13">
       <c r="C23" s="44" t="s">
         <v>113</v>
       </c>
@@ -7398,7 +7422,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="27" spans="1:12">
+    <row r="27" spans="1:12" ht="13">
       <c r="C27" s="61" t="s">
         <v>126</v>
       </c>
@@ -7491,12 +7515,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="32" spans="1:12">
+    <row r="32" spans="1:12" ht="13">
       <c r="A32" s="97" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="33" spans="1:5" s="97" customFormat="1">
+    <row r="33" spans="1:5" s="97" customFormat="1" ht="13">
       <c r="A33" s="77" t="s">
         <v>217</v>
       </c>
@@ -7523,6 +7547,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="C10:C13"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="C15:C18"/>
+    <mergeCell ref="G15:G16"/>
     <mergeCell ref="I15:I16"/>
     <mergeCell ref="A17:A18"/>
     <mergeCell ref="A1:D1"/>
@@ -7530,11 +7559,6 @@
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="I3:I4"/>
     <mergeCell ref="C5:C8"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="C10:C13"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="C15:C18"/>
-    <mergeCell ref="G15:G16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="89" orientation="landscape" r:id="rId1"/>
